--- a/outputs/comercial/auditoria/Agenda_Renovacoes.xlsx
+++ b/outputs/comercial/auditoria/Agenda_Renovacoes.xlsx
@@ -577,27 +577,27 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>80940244550</t>
+          <t>68011280598</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>45829</v>
+        <v>45834</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>46194</v>
+        <v>46199</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>3833.76</v>
+        <v>5218.51</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>460.05</v>
+        <v>782.78</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" s="3" t="b">
         <v>1</v>
@@ -620,39 +620,39 @@
         <v>1</v>
       </c>
       <c r="M2" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O2" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>81273585730</t>
+          <t>76617711592</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>45829</v>
+        <v>45841</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>46194</v>
+        <v>46206</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0</v>
+        <v>7049.86</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>917.71</v>
+        <v>704.99</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>3</v>
@@ -675,39 +675,39 @@
         <v>1</v>
       </c>
       <c r="M3" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O3" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>68011280598</t>
+          <t>25534192832</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>45834</v>
+        <v>45851</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>46199</v>
+        <v>46216</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5218.51</v>
+        <v>2594.16</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>782.78</v>
+        <v>259.42</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1</v>
@@ -730,19 +730,19 @@
         <v>1</v>
       </c>
       <c r="M4" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O4" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>76617711592</t>
+          <t>08240433504</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>45841</v>
+        <v>45852</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>46206</v>
+        <v>46217</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>7049.86</v>
+        <v>8271.17</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>704.99</v>
+        <v>1488.81</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>3</v>
@@ -797,12 +797,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>25534192832</t>
+          <t>15890429025</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>45851</v>
+        <v>45854</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>23</v>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2594.16</v>
+        <v>8452.059999999999</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>259.42</v>
+        <v>1267.81</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" s="3" t="b">
         <v>1</v>
@@ -852,41 +852,41 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>08240433504</t>
+          <t>63942788165</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>45852</v>
+        <v>45862</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>46217</v>
+        <v>46227</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>🔴 Até 30 dias</t>
+          <t>🟡 31 a 60 dias</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>8271.17</v>
+        <v>6461.01</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1488.81</v>
+        <v>1292.2</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" s="5" t="b">
         <v>1</v>
@@ -907,41 +907,41 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>15890429025</t>
+          <t>85642059304</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>45854</v>
+        <v>45862</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>46219</v>
+        <v>46227</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>🔴 Até 30 dias</t>
+          <t>🟡 31 a 60 dias</t>
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>8452.059999999999</v>
+        <v>2764.94</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1267.81</v>
+        <v>414.74</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8" s="3" t="b">
         <v>1</v>
@@ -950,39 +950,39 @@
         <v>1</v>
       </c>
       <c r="M8" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O8" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>63942788165</t>
+          <t>13858542493</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>45862</v>
+        <v>45866</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -990,13 +990,13 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>6461.01</v>
+        <v>3425.27</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1292.2</v>
+        <v>411.03</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="5" t="b">
         <v>1</v>
@@ -1005,39 +1005,39 @@
         <v>1</v>
       </c>
       <c r="M9" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O9" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>85642059304</t>
+          <t>56704310385</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>45862</v>
+        <v>45866</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>2764.94</v>
+        <v>323.15</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>414.74</v>
+        <v>96.94</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>1</v>
@@ -1072,27 +1072,27 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>13858542493</t>
+          <t>91846386557</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>45866</v>
+        <v>45867</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>3425.27</v>
+        <v>403.86</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>411.03</v>
+        <v>72.69</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" s="5" t="b">
         <v>1</v>
@@ -1115,39 +1115,39 @@
         <v>1</v>
       </c>
       <c r="M11" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O11" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>56704310385</t>
+          <t>89026012796</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>45866</v>
+        <v>45870</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>46231</v>
+        <v>46235</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>323.15</v>
+        <v>3165.12</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>96.94</v>
+        <v>379.81</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>1</v>
@@ -1182,27 +1182,27 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>58514936899</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>45867</v>
+        <v>45872</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
@@ -1210,13 +1210,13 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>403.86</v>
+        <v>7580.02</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>72.69</v>
+        <v>4323.47</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="5" t="b">
         <v>1</v>
@@ -1225,39 +1225,39 @@
         <v>1</v>
       </c>
       <c r="M13" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O13" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>89026012796</t>
+          <t>28699041379</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>45870</v>
+        <v>45876</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>3165.12</v>
+        <v>458.71</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>379.81</v>
+        <v>68.81</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K14" s="3" t="b">
         <v>1</v>
@@ -1292,27 +1292,27 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>58514936899</t>
+          <t>47284639208</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>45872</v>
+        <v>45877</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>7580.02</v>
+        <v>7846.91</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>4323.47</v>
+        <v>1683.32</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>3</v>
@@ -1347,12 +1347,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>28699041379</t>
+          <t>95701543039</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>45876</v>
+        <v>45881</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>458.71</v>
+        <v>4025.31</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>68.81</v>
+        <v>724.5599999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>1</v>
@@ -1402,12 +1402,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>47284639208</t>
+          <t>12499856984</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>45877</v>
+        <v>45883</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>46242</v>
+        <v>46248</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>7846.91</v>
+        <v>5693.24</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>1683.32</v>
+        <v>853.99</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>3</v>
@@ -1445,39 +1445,39 @@
         <v>1</v>
       </c>
       <c r="M17" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O17" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>95701543039</t>
+          <t>19148564679</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>45881</v>
+        <v>45883</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>4025.31</v>
+        <v>8370.52</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>724.5599999999999</v>
+        <v>1506.69</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3</v>
@@ -1500,39 +1500,39 @@
         <v>1</v>
       </c>
       <c r="M18" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O18" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>12499856984</t>
+          <t>26011939103</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>45883</v>
+        <v>45884</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
@@ -1540,51 +1540,51 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>5693.24</v>
+        <v>2231.56</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>853.99</v>
+        <v>669.47</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>19148564679</t>
+          <t>91846386557</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>45883</v>
+        <v>45886</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>55</v>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>8370.52</v>
+        <v>8185.23</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1506.69</v>
+        <v>982.23</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="3" t="b">
         <v>1</v>
@@ -1610,24 +1610,24 @@
         <v>1</v>
       </c>
       <c r="M20" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O20" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>26011939103</t>
+          <t>62003424420</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>45884</v>
+        <v>45889</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>46249</v>
+        <v>46254</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
@@ -1650,25 +1650,25 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>2231.56</v>
+        <v>4243.38</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>669.47</v>
+        <v>848.6799999999999</v>
       </c>
       <c r="J21" s="5" t="n">
         <v>2</v>
       </c>
       <c r="K21" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="5" t="b">
         <v>0</v>
       </c>
       <c r="N21" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="5" t="b">
         <v>0</v>
@@ -1677,27 +1677,27 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>52056647423</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>45886</v>
+        <v>45891</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>46251</v>
+        <v>46256</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8185.23</v>
+        <v>3293.99</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>982.23</v>
+        <v>4973.87</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="3" t="b">
         <v>1</v>
@@ -1732,7 +1732,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>62003424420</t>
+          <t>08589944171</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1742,14 +1742,14 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>45889</v>
+        <v>45892</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>61</v>
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>4243.38</v>
+        <v>1616.84</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>848.6799999999999</v>
+        <v>404.21</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="5" t="b">
         <v>1</v>
@@ -1775,39 +1775,39 @@
         <v>1</v>
       </c>
       <c r="M23" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O23" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>52056647423</t>
+          <t>24051477053</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>45891</v>
+        <v>45897</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>46256</v>
+        <v>46262</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>3293.99</v>
+        <v>3443.15</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>4973.87</v>
+        <v>413.18</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>1</v>
@@ -1842,7 +1842,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>08589944171</t>
+          <t>37562890028</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1852,17 +1852,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>45892</v>
+        <v>45750</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>46257</v>
+        <v>46263</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>1616.84</v>
+        <v>6019.52</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>404.21</v>
+        <v>1447.99</v>
       </c>
       <c r="J25" s="5" t="n">
         <v>3</v>
@@ -1885,36 +1885,36 @@
         <v>1</v>
       </c>
       <c r="M25" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O25" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>24051477053</t>
+          <t>62244472126</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>45897</v>
+        <v>45900</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>69</v>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>3443.15</v>
+        <v>3848.65</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>413.18</v>
+        <v>769.73</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>1</v>
@@ -1940,19 +1940,19 @@
         <v>1</v>
       </c>
       <c r="M26" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O26" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>37562890028</t>
+          <t>87258874495</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -1966,13 +1966,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>45750</v>
+        <v>45900</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>6019.52</v>
+        <v>4433.94</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>1447.99</v>
+        <v>886.79</v>
       </c>
       <c r="J27" s="5" t="n">
         <v>3</v>
@@ -2007,12 +2007,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>62244472126</t>
+          <t>38657191826</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2021,13 +2021,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>45900</v>
+        <v>45902</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -2035,13 +2035,13 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>3848.65</v>
+        <v>7115.43</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>769.73</v>
+        <v>1423.09</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K28" s="3" t="b">
         <v>1</v>
@@ -2062,7 +2062,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>87258874495</t>
+          <t>71657262849</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2076,13 +2076,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>45900</v>
+        <v>45904</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>4433.94</v>
+        <v>3843.36</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>886.79</v>
+        <v>5041.73</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K29" s="5" t="b">
         <v>1</v>
@@ -2117,27 +2117,27 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>38657191826</t>
+          <t>70335211039</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>45902</v>
+        <v>45906</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>46267</v>
+        <v>46271</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>7115.43</v>
+        <v>9184.860000000001</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1423.09</v>
+        <v>1377.72</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="3" t="b">
         <v>1</v>
@@ -2172,7 +2172,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>71657262849</t>
+          <t>42836440892</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>45904</v>
+        <v>45911</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>3843.36</v>
+        <v>5525.39</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>5041.73</v>
+        <v>663.05</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31" s="5" t="b">
         <v>1</v>
@@ -2227,27 +2227,27 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>70335211039</t>
+          <t>74783667428</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>45906</v>
+        <v>45912</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>46271</v>
+        <v>46277</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>9184.860000000001</v>
+        <v>2742.66</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1377.72</v>
+        <v>329.12</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>1</v>
@@ -2282,27 +2282,27 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>42836440892</t>
+          <t>75901751863</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>45911</v>
+        <v>45913</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>5525.39</v>
+        <v>6204.82</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>663.05</v>
+        <v>930.72</v>
       </c>
       <c r="J33" s="5" t="n">
         <v>3</v>
@@ -2337,24 +2337,24 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>74783667428</t>
+          <t>15313636317</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>84</v>
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>2742.66</v>
+        <v>3908.5</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>329.12</v>
+        <v>1637.11</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K34" s="3" t="b">
         <v>1</v>
@@ -2392,12 +2392,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>75901751863</t>
+          <t>51713395962</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>45913</v>
+        <v>45873</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>46278</v>
+        <v>46281</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>85</v>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>6204.82</v>
+        <v>12502.32</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>930.72</v>
+        <v>3346.76</v>
       </c>
       <c r="J35" s="5" t="n">
         <v>3</v>
@@ -2447,27 +2447,27 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>15313636317</t>
+          <t>78292216995</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>3908.5</v>
+        <v>4494.66</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1637.11</v>
+        <v>539.36</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>3</v>
@@ -2490,24 +2490,24 @@
         <v>1</v>
       </c>
       <c r="M36" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O36" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>51713395962</t>
+          <t>54868740345</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2516,13 +2516,13 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>45873</v>
+        <v>45918</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>12502.32</v>
+        <v>498.86</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>3346.76</v>
+        <v>74.83</v>
       </c>
       <c r="J37" s="5" t="n">
         <v>3</v>
@@ -2545,36 +2545,36 @@
         <v>1</v>
       </c>
       <c r="M37" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O37" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>78292216995</t>
+          <t>45547813767</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>45917</v>
+        <v>45920</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>46282</v>
+        <v>46285</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>89</v>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>4494.66</v>
+        <v>4191.78</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>539.36</v>
+        <v>838.36</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K38" s="3" t="b">
         <v>1</v>
@@ -2612,7 +2612,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>54868740345</t>
+          <t>85368663266</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -2622,14 +2622,14 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>45918</v>
+        <v>45921</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>90</v>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>498.86</v>
+        <v>4188.14</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>74.83</v>
+        <v>1407.64</v>
       </c>
       <c r="J39" s="5" t="n">
         <v>3</v>
@@ -2655,13 +2655,13 @@
         <v>1</v>
       </c>
       <c r="M39" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O39" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5750,7 +5750,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>PROD-002378</t>
+          <t>PROD-002432</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -5759,48 +5759,48 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2378</v>
+        <v>2432</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>80940244550</t>
+          <t>54868740345</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>45829</v>
+        <v>45918</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>120477</v>
+        <v>964314</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>45829</v>
+        <v>45918</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>46194</v>
+        <v>46283</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -5827,84 +5827,84 @@
       <c r="S19" s="5" t="inlineStr"/>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t>Eduardo Costa</t>
+          <t>Sérgio Gomes</t>
         </is>
       </c>
       <c r="U19" s="5" t="n">
-        <v>80940244550</v>
+        <v>54868740345</v>
       </c>
       <c r="V19" s="5" t="n">
-        <v>2013391</v>
+        <v>3767919</v>
       </c>
       <c r="W19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>3833.76</v>
+        <v>498.86</v>
       </c>
       <c r="Y19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z19" s="5" t="n">
+        <v>74.83</v>
+      </c>
+      <c r="AA19" s="5" t="inlineStr">
+        <is>
+          <t>Corretor Exemplo</t>
+        </is>
+      </c>
+      <c r="AB19" s="6" t="n">
+        <v>45918</v>
+      </c>
+      <c r="AC19" s="6" t="n">
+        <v>45918</v>
+      </c>
+      <c r="AD19" s="5" t="n">
+        <v>74.83</v>
+      </c>
+      <c r="AE19" s="5" t="inlineStr">
+        <is>
+          <t>usuario.exemplo</t>
+        </is>
+      </c>
+      <c r="AF19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="5" t="n">
         <v>12</v>
-      </c>
-      <c r="Z19" s="5" t="n">
-        <v>460.05</v>
-      </c>
-      <c r="AA19" s="5" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="AB19" s="6" t="n">
-        <v>45829</v>
-      </c>
-      <c r="AC19" s="6" t="n">
-        <v>45829</v>
-      </c>
-      <c r="AD19" s="5" t="n">
-        <v>460.05</v>
-      </c>
-      <c r="AE19" s="5" t="inlineStr">
-        <is>
-          <t>usuario.exemplo</t>
-        </is>
-      </c>
-      <c r="AF19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="AH19" s="5" t="inlineStr"/>
       <c r="AI19" s="5" t="inlineStr"/>
       <c r="AJ19" s="5" t="n">
-        <v>531944</v>
+        <v>894360</v>
       </c>
       <c r="AK19" s="5" t="inlineStr"/>
       <c r="AL19" s="6" t="n">
-        <v>45829</v>
+        <v>45918</v>
       </c>
       <c r="AM19" s="5" t="inlineStr"/>
       <c r="AN19" s="6" t="n">
-        <v>45829</v>
+        <v>45918</v>
       </c>
       <c r="AO19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP19" s="5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AQ19" s="5" t="inlineStr">
         <is>
-          <t>Clínica Médica</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="AR19" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL - Plano Exemplo</t>
+          <t>RESIDENCIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS19" s="5" t="inlineStr">
         <is>
-          <t>2013391</t>
+          <t>3767919</t>
         </is>
       </c>
       <c r="AT19" s="5" t="b">
@@ -5914,7 +5914,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>PROD-002432</t>
+          <t>PROD-002786</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -5923,48 +5923,48 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2432</v>
+        <v>2786</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>54868740345</t>
+          <t>63942788165</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>964314</v>
+        <v>801613</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>46283</v>
+        <v>46227</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -5991,26 +5991,26 @@
       <c r="S20" s="3" t="inlineStr"/>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>Sérgio Gomes</t>
+          <t>Helena Silva</t>
         </is>
       </c>
       <c r="U20" s="3" t="n">
-        <v>54868740345</v>
+        <v>63942788165</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>3767919</v>
+        <v>49823142025</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>498.86</v>
+        <v>6461.01</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>74.83</v>
+        <v>1292.2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -6018,13 +6018,13 @@
         </is>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="AC20" s="4" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>74.83</v>
+        <v>1292.2</v>
       </c>
       <c r="AE20" s="3" t="inlineStr">
         <is>
@@ -6035,40 +6035,40 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH20" s="3" t="inlineStr"/>
       <c r="AI20" s="3" t="inlineStr"/>
       <c r="AJ20" s="3" t="n">
-        <v>894360</v>
+        <v>102557</v>
       </c>
       <c r="AK20" s="3" t="inlineStr"/>
       <c r="AL20" s="4" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="AM20" s="3" t="inlineStr"/>
       <c r="AN20" s="4" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP20" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>Urologia</t>
+          <t>Psiquiatria</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL - Plano Exemplo</t>
+          <t>EQUIPAMENTOS - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>3767919</t>
+          <t>4982314</t>
         </is>
       </c>
       <c r="AT20" s="3" t="b">
@@ -6078,7 +6078,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>PROD-002786</t>
+          <t>PROD-002787</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -6087,38 +6087,38 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2786</v>
+        <v>2787</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>63942788165</t>
+          <t>85642059304</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="I21" s="6" t="n">
         <v>45862</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>801613</v>
+        <v>360535</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>45862</v>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
@@ -6155,26 +6155,26 @@
       <c r="S21" s="5" t="inlineStr"/>
       <c r="T21" s="5" t="inlineStr">
         <is>
-          <t>Helena Silva</t>
+          <t>Olívia Rodrigues</t>
         </is>
       </c>
       <c r="U21" s="5" t="n">
-        <v>63942788165</v>
+        <v>85642059304</v>
       </c>
       <c r="V21" s="5" t="n">
-        <v>49823142025</v>
+        <v>8546302</v>
       </c>
       <c r="W21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>6461.01</v>
+        <v>2764.94</v>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z21" s="5" t="n">
-        <v>1292.2</v>
+        <v>414.74</v>
       </c>
       <c r="AA21" s="5" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45862</v>
       </c>
       <c r="AD21" s="5" t="n">
-        <v>1292.2</v>
+        <v>414.74</v>
       </c>
       <c r="AE21" s="5" t="inlineStr">
         <is>
@@ -6199,12 +6199,12 @@
         <v>0</v>
       </c>
       <c r="AG21" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH21" s="5" t="inlineStr"/>
       <c r="AI21" s="5" t="inlineStr"/>
       <c r="AJ21" s="5" t="n">
-        <v>102557</v>
+        <v>553275</v>
       </c>
       <c r="AK21" s="5" t="inlineStr"/>
       <c r="AL21" s="6" t="n">
@@ -6218,21 +6218,21 @@
         <v>1</v>
       </c>
       <c r="AP21" s="5" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AQ21" s="5" t="inlineStr">
         <is>
-          <t>Psiquiatria</t>
+          <t>Oftalmologia</t>
         </is>
       </c>
       <c r="AR21" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS - Plano Exemplo</t>
+          <t>RC PROFISSIONAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS21" s="5" t="inlineStr">
         <is>
-          <t>4982314</t>
+          <t>8546302</t>
         </is>
       </c>
       <c r="AT21" s="5" t="b">
@@ -6242,7 +6242,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>PROD-002787</t>
+          <t>PROD-003286</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -6251,48 +6251,48 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2787</v>
+        <v>3286</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>85642059304</t>
+          <t>76617711592</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>360535</v>
+        <v>468934</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>46227</v>
+        <v>46206</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -6308,7 +6308,7 @@
       <c r="P22" s="3" t="inlineStr"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -6319,26 +6319,26 @@
       <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>Olívia Rodrigues</t>
+          <t>Paulo Pereira</t>
         </is>
       </c>
       <c r="U22" s="3" t="n">
-        <v>85642059304</v>
+        <v>76617711592</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>8546302</v>
+        <v>7129228</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>2764.94</v>
+        <v>7049.86</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>414.74</v>
+        <v>704.99</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -6346,13 +6346,13 @@
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="AC22" s="4" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>414.74</v>
+        <v>704.99</v>
       </c>
       <c r="AE22" s="3" t="inlineStr">
         <is>
@@ -6368,35 +6368,35 @@
       <c r="AH22" s="3" t="inlineStr"/>
       <c r="AI22" s="3" t="inlineStr"/>
       <c r="AJ22" s="3" t="n">
-        <v>553275</v>
+        <v>764704</v>
       </c>
       <c r="AK22" s="3" t="inlineStr"/>
       <c r="AL22" s="4" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="AM22" s="3" t="inlineStr"/>
       <c r="AN22" s="4" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP22" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>Oftalmologia</t>
+          <t>Radiologia</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL - Plano Exemplo</t>
+          <t>EMPRESARIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>8546302</t>
+          <t>7129228</t>
         </is>
       </c>
       <c r="AT22" s="3" t="b">
@@ -6406,7 +6406,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>PROD-003286</t>
+          <t>PROD-003542</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -6415,48 +6415,48 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>3286</v>
+        <v>3542</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>76617711592</t>
+          <t>37562890028</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I23" s="6" t="n">
-        <v>45841</v>
+        <v>45750</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>468934</v>
+        <v>622379</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>45841</v>
+        <v>45750</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>46206</v>
+        <v>46115</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -6483,26 +6483,26 @@
       <c r="S23" s="5" t="inlineStr"/>
       <c r="T23" s="5" t="inlineStr">
         <is>
-          <t>Paulo Pereira</t>
+          <t>Ana Oliveira</t>
         </is>
       </c>
       <c r="U23" s="5" t="n">
-        <v>76617711592</v>
+        <v>37562890028</v>
       </c>
       <c r="V23" s="5" t="n">
-        <v>7129228</v>
+        <v>5420147</v>
       </c>
       <c r="W23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X23" s="5" t="n">
-        <v>7049.86</v>
+        <v>2440.79</v>
       </c>
       <c r="Y23" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="Z23" s="5" t="n">
-        <v>704.99</v>
+        <v>732.24</v>
       </c>
       <c r="AA23" s="5" t="inlineStr">
         <is>
@@ -6510,13 +6510,13 @@
         </is>
       </c>
       <c r="AB23" s="6" t="n">
-        <v>45841</v>
+        <v>45750</v>
       </c>
       <c r="AC23" s="6" t="n">
-        <v>45841</v>
+        <v>45750</v>
       </c>
       <c r="AD23" s="5" t="n">
-        <v>704.99</v>
+        <v>732.24</v>
       </c>
       <c r="AE23" s="5" t="inlineStr">
         <is>
@@ -6532,35 +6532,35 @@
       <c r="AH23" s="5" t="inlineStr"/>
       <c r="AI23" s="5" t="inlineStr"/>
       <c r="AJ23" s="5" t="n">
-        <v>764704</v>
+        <v>652819</v>
       </c>
       <c r="AK23" s="5" t="inlineStr"/>
       <c r="AL23" s="6" t="n">
-        <v>45841</v>
+        <v>45750</v>
       </c>
       <c r="AM23" s="5" t="inlineStr"/>
       <c r="AN23" s="6" t="n">
-        <v>45841</v>
+        <v>45750</v>
       </c>
       <c r="AO23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP23" s="5" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AQ23" s="5" t="inlineStr">
         <is>
-          <t>Radiologia</t>
+          <t>Psiquiatria</t>
         </is>
       </c>
       <c r="AR23" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS23" s="5" t="inlineStr">
         <is>
-          <t>7129228</t>
+          <t>5420147</t>
         </is>
       </c>
       <c r="AT23" s="5" t="b">
@@ -6570,7 +6570,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>PROD-003542</t>
+          <t>PROD-003561</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6579,48 +6579,48 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>3542</v>
+        <v>3561</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>37562890028</t>
+          <t>75901751863</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>45750</v>
+        <v>45913</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>622379</v>
+        <v>923620</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>45750</v>
+        <v>45913</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>46115</v>
+        <v>46278</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -6636,7 +6636,7 @@
       <c r="P24" s="3" t="inlineStr"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
@@ -6647,26 +6647,26 @@
       <c r="S24" s="3" t="inlineStr"/>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>Ana Oliveira</t>
+          <t>Júlia Lima</t>
         </is>
       </c>
       <c r="U24" s="3" t="n">
-        <v>37562890028</v>
+        <v>75901751863</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>5420147</v>
+        <v>2171603</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>2440.79</v>
+        <v>6204.82</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>732.24</v>
+        <v>930.72</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -6674,13 +6674,13 @@
         </is>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>45750</v>
+        <v>45913</v>
       </c>
       <c r="AC24" s="4" t="n">
-        <v>45750</v>
+        <v>45913</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>732.24</v>
+        <v>930.72</v>
       </c>
       <c r="AE24" s="3" t="inlineStr">
         <is>
@@ -6691,40 +6691,40 @@
         <v>0</v>
       </c>
       <c r="AG24" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH24" s="3" t="inlineStr"/>
       <c r="AI24" s="3" t="inlineStr"/>
       <c r="AJ24" s="3" t="n">
-        <v>652819</v>
+        <v>452700</v>
       </c>
       <c r="AK24" s="3" t="inlineStr"/>
       <c r="AL24" s="4" t="n">
-        <v>45750</v>
+        <v>45913</v>
       </c>
       <c r="AM24" s="3" t="inlineStr"/>
       <c r="AN24" s="4" t="n">
-        <v>45750</v>
+        <v>45913</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP24" s="3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>Psiquiatria</t>
+          <t>Radiologia</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL - Plano Exemplo</t>
+          <t>RESIDENCIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>5420147</t>
+          <t>2171603</t>
         </is>
       </c>
       <c r="AT24" s="3" t="b">
@@ -6734,7 +6734,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>PROD-003561</t>
+          <t>PROD-003785</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -6743,11 +6743,11 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>3561</v>
+        <v>3785</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>75901751863</t>
+          <t>56704310385</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -6757,30 +6757,30 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="I25" s="6" t="n">
-        <v>45913</v>
+        <v>45866</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>923620</v>
+        <v>469093</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>45913</v>
+        <v>45866</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>46278</v>
+        <v>46231</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
       <c r="P25" s="5" t="inlineStr"/>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R25" s="5" t="inlineStr">
@@ -6811,26 +6811,26 @@
       <c r="S25" s="5" t="inlineStr"/>
       <c r="T25" s="5" t="inlineStr">
         <is>
-          <t>Júlia Lima</t>
+          <t>Bruno Gomes</t>
         </is>
       </c>
       <c r="U25" s="5" t="n">
-        <v>75901751863</v>
+        <v>56704310385</v>
       </c>
       <c r="V25" s="5" t="n">
-        <v>2171603</v>
+        <v>6558135</v>
       </c>
       <c r="W25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X25" s="5" t="n">
-        <v>6204.82</v>
+        <v>323.15</v>
       </c>
       <c r="Y25" s="5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="Z25" s="5" t="n">
-        <v>930.72</v>
+        <v>96.94</v>
       </c>
       <c r="AA25" s="5" t="inlineStr">
         <is>
@@ -6838,13 +6838,13 @@
         </is>
       </c>
       <c r="AB25" s="6" t="n">
-        <v>45913</v>
+        <v>45866</v>
       </c>
       <c r="AC25" s="6" t="n">
-        <v>45913</v>
+        <v>45866</v>
       </c>
       <c r="AD25" s="5" t="n">
-        <v>930.72</v>
+        <v>96.94</v>
       </c>
       <c r="AE25" s="5" t="inlineStr">
         <is>
@@ -6860,35 +6860,35 @@
       <c r="AH25" s="5" t="inlineStr"/>
       <c r="AI25" s="5" t="inlineStr"/>
       <c r="AJ25" s="5" t="n">
-        <v>452700</v>
+        <v>270751</v>
       </c>
       <c r="AK25" s="5" t="inlineStr"/>
       <c r="AL25" s="6" t="n">
-        <v>45913</v>
+        <v>45866</v>
       </c>
       <c r="AM25" s="5" t="inlineStr"/>
       <c r="AN25" s="6" t="n">
-        <v>45913</v>
+        <v>45866</v>
       </c>
       <c r="AO25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP25" s="5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AQ25" s="5" t="inlineStr">
         <is>
-          <t>Radiologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="AR25" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL - Plano Exemplo</t>
+          <t>EQUIPAMENTOS - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS25" s="5" t="inlineStr">
         <is>
-          <t>2171603</t>
+          <t>6558135</t>
         </is>
       </c>
       <c r="AT25" s="5" t="b">
@@ -6898,7 +6898,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>PROD-003692</t>
+          <t>PROD-004086</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6907,48 +6907,48 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3692</v>
+        <v>4086</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>81273585730</t>
+          <t>08589944171</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>45829</v>
+        <v>45892</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>433401</v>
+        <v>474147</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>45829</v>
+        <v>45892</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>46194</v>
+        <v>46257</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -6964,7 +6964,7 @@
       <c r="P26" s="3" t="inlineStr"/>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
@@ -6975,26 +6975,26 @@
       <c r="S26" s="3" t="inlineStr"/>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>Gabriel Barbosa</t>
+          <t>Carla Souza</t>
         </is>
       </c>
       <c r="U26" s="3" t="n">
-        <v>81273585730</v>
+        <v>8589944171</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>48919302025</v>
+        <v>3480382</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>0</v>
+        <v>1616.84</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>917.71</v>
+        <v>404.21</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -7002,13 +7002,13 @@
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>45829</v>
+        <v>45892</v>
       </c>
       <c r="AC26" s="4" t="n">
-        <v>45829</v>
+        <v>45892</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>917.71</v>
+        <v>404.21</v>
       </c>
       <c r="AE26" s="3" t="inlineStr">
         <is>
@@ -7019,40 +7019,40 @@
         <v>0</v>
       </c>
       <c r="AG26" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH26" s="3" t="inlineStr"/>
       <c r="AI26" s="3" t="inlineStr"/>
       <c r="AJ26" s="3" t="n">
-        <v>702278</v>
+        <v>936111</v>
       </c>
       <c r="AK26" s="3" t="inlineStr"/>
       <c r="AL26" s="4" t="n">
-        <v>45829</v>
+        <v>45892</v>
       </c>
       <c r="AM26" s="3" t="inlineStr"/>
       <c r="AN26" s="4" t="n">
-        <v>45829</v>
+        <v>45892</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP26" s="3" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>Neurologia</t>
+          <t>Oftalmologia</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS - Plano Exemplo</t>
+          <t>RESIDENCIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>4891930</t>
+          <t>3480382</t>
         </is>
       </c>
       <c r="AT26" s="3" t="b">
@@ -7062,7 +7062,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>PROD-003785</t>
+          <t>PROD-004140</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -7071,11 +7071,11 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>3785</v>
+        <v>4140</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>56704310385</t>
+          <t>08240433504</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -7085,30 +7085,30 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="I27" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>469093</v>
+        <v>628741</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>46231</v>
+        <v>46217</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
       <c r="P27" s="5" t="inlineStr"/>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R27" s="5" t="inlineStr">
@@ -7139,26 +7139,26 @@
       <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="5" t="inlineStr">
         <is>
-          <t>Bruno Gomes</t>
+          <t>Yara Souza</t>
         </is>
       </c>
       <c r="U27" s="5" t="n">
-        <v>56704310385</v>
+        <v>8240433504</v>
       </c>
       <c r="V27" s="5" t="n">
-        <v>6558135</v>
+        <v>9813864</v>
       </c>
       <c r="W27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X27" s="5" t="n">
-        <v>323.15</v>
+        <v>8271.17</v>
       </c>
       <c r="Y27" s="5" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="Z27" s="5" t="n">
-        <v>96.94</v>
+        <v>1488.81</v>
       </c>
       <c r="AA27" s="5" t="inlineStr">
         <is>
@@ -7166,13 +7166,13 @@
         </is>
       </c>
       <c r="AB27" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="AC27" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="AD27" s="5" t="n">
-        <v>96.94</v>
+        <v>1488.81</v>
       </c>
       <c r="AE27" s="5" t="inlineStr">
         <is>
@@ -7183,26 +7183,26 @@
         <v>0</v>
       </c>
       <c r="AG27" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH27" s="5" t="inlineStr"/>
       <c r="AI27" s="5" t="inlineStr"/>
       <c r="AJ27" s="5" t="n">
-        <v>270751</v>
+        <v>763637</v>
       </c>
       <c r="AK27" s="5" t="inlineStr"/>
       <c r="AL27" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="AM27" s="5" t="inlineStr"/>
       <c r="AN27" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="AO27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP27" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AQ27" s="5" t="inlineStr">
         <is>
@@ -7211,12 +7211,12 @@
       </c>
       <c r="AR27" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS - Plano Exemplo</t>
+          <t>EMPRESARIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS27" s="5" t="inlineStr">
         <is>
-          <t>6558135</t>
+          <t>9813864</t>
         </is>
       </c>
       <c r="AT27" s="5" t="b">
@@ -7226,7 +7226,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>PROD-004086</t>
+          <t>PROD-004320</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -7235,21 +7235,21 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4086</v>
+        <v>4320</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>08589944171</t>
+          <t>38657191826</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -7259,24 +7259,24 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>474147</v>
+        <v>442395</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>46257</v>
+        <v>46267</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -7303,26 +7303,26 @@
       <c r="S28" s="3" t="inlineStr"/>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>Carla Souza</t>
+          <t>Ana Almeida</t>
         </is>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8589944171</v>
+        <v>38657191826</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>3480382</v>
+        <v>7314480</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>1616.84</v>
+        <v>7115.43</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>404.21</v>
+        <v>1423.09</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -7330,13 +7330,13 @@
         </is>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="AC28" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>404.21</v>
+        <v>1423.09</v>
       </c>
       <c r="AE28" s="3" t="inlineStr">
         <is>
@@ -7347,40 +7347,40 @@
         <v>0</v>
       </c>
       <c r="AG28" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH28" s="3" t="inlineStr"/>
       <c r="AI28" s="3" t="inlineStr"/>
       <c r="AJ28" s="3" t="n">
-        <v>936111</v>
+        <v>516129</v>
       </c>
       <c r="AK28" s="3" t="inlineStr"/>
       <c r="AL28" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="AM28" s="3" t="inlineStr"/>
       <c r="AN28" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP28" s="3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>Oftalmologia</t>
+          <t>Ginecologia e Obstetrícia</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>3480382</t>
+          <t>7314480</t>
         </is>
       </c>
       <c r="AT28" s="3" t="b">
@@ -7390,7 +7390,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>PROD-004140</t>
+          <t>PROD-004379</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -7399,11 +7399,11 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>4140</v>
+        <v>4379</v>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>08240433504</t>
+          <t>85368663266</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -7423,20 +7423,20 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I29" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>628741</v>
+        <v>877005</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>46217</v>
+        <v>46286</v>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
       <c r="P29" s="5" t="inlineStr"/>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr">
@@ -7467,26 +7467,26 @@
       <c r="S29" s="5" t="inlineStr"/>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t>Yara Souza</t>
+          <t>Rafaela Lima</t>
         </is>
       </c>
       <c r="U29" s="5" t="n">
-        <v>8240433504</v>
+        <v>85368663266</v>
       </c>
       <c r="V29" s="5" t="n">
-        <v>9813864</v>
+        <v>3572267</v>
       </c>
       <c r="W29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X29" s="5" t="n">
-        <v>8271.17</v>
+        <v>4188.14</v>
       </c>
       <c r="Y29" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z29" s="5" t="n">
-        <v>1488.81</v>
+        <v>1407.64</v>
       </c>
       <c r="AA29" s="5" t="inlineStr">
         <is>
@@ -7494,13 +7494,13 @@
         </is>
       </c>
       <c r="AB29" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="AC29" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="AD29" s="5" t="n">
-        <v>1488.81</v>
+        <v>1407.64</v>
       </c>
       <c r="AE29" s="5" t="inlineStr">
         <is>
@@ -7516,35 +7516,35 @@
       <c r="AH29" s="5" t="inlineStr"/>
       <c r="AI29" s="5" t="inlineStr"/>
       <c r="AJ29" s="5" t="n">
-        <v>763637</v>
+        <v>515999</v>
       </c>
       <c r="AK29" s="5" t="inlineStr"/>
       <c r="AL29" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="AM29" s="5" t="inlineStr"/>
       <c r="AN29" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="AO29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP29" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AQ29" s="5" t="inlineStr">
         <is>
-          <t>Endocrinologia</t>
+          <t>Psiquiatria</t>
         </is>
       </c>
       <c r="AR29" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS29" s="5" t="inlineStr">
         <is>
-          <t>9813864</t>
+          <t>3572267</t>
         </is>
       </c>
       <c r="AT29" s="5" t="b">
@@ -7554,7 +7554,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>PROD-004320</t>
+          <t>PROD-004386</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -7563,48 +7563,48 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4320</v>
+        <v>4386</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>38657191826</t>
+          <t>89026012796</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>442395</v>
+        <v>842857</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>46267</v>
+        <v>46235</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7631,26 +7631,26 @@
       <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>Ana Almeida</t>
+          <t>Olívia Souza</t>
         </is>
       </c>
       <c r="U30" s="3" t="n">
-        <v>38657191826</v>
+        <v>89026012796</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>7314480</v>
+        <v>9154494</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>7115.43</v>
+        <v>3165.12</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>1423.09</v>
+        <v>379.81</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -7658,13 +7658,13 @@
         </is>
       </c>
       <c r="AB30" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="AC30" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="AD30" s="3" t="n">
-        <v>1423.09</v>
+        <v>379.81</v>
       </c>
       <c r="AE30" s="3" t="inlineStr">
         <is>
@@ -7675,40 +7675,40 @@
         <v>0</v>
       </c>
       <c r="AG30" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH30" s="3" t="inlineStr"/>
       <c r="AI30" s="3" t="inlineStr"/>
       <c r="AJ30" s="3" t="n">
-        <v>516129</v>
+        <v>964618</v>
       </c>
       <c r="AK30" s="3" t="inlineStr"/>
       <c r="AL30" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="AM30" s="3" t="inlineStr"/>
       <c r="AN30" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP30" s="3" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>Ginecologia e Obstetrícia</t>
+          <t>Cirurgia Geral</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL - Plano Exemplo</t>
+          <t>RESIDENCIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>7314480</t>
+          <t>9154494</t>
         </is>
       </c>
       <c r="AT30" s="3" t="b">
@@ -7718,7 +7718,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>PROD-004386</t>
+          <t>PROD-004406</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -7727,11 +7727,11 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>4386</v>
+        <v>4406</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>89026012796</t>
+          <t>91846386557</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -7741,30 +7741,30 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="I31" s="6" t="n">
-        <v>45870</v>
+        <v>45886</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>842857</v>
+        <v>901247</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>45870</v>
+        <v>45886</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>46235</v>
+        <v>46251</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
       <c r="P31" s="5" t="inlineStr"/>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R31" s="5" t="inlineStr">
@@ -7795,26 +7795,26 @@
       <c r="S31" s="5" t="inlineStr"/>
       <c r="T31" s="5" t="inlineStr">
         <is>
-          <t>Olívia Souza</t>
+          <t>Helena Gomes</t>
         </is>
       </c>
       <c r="U31" s="5" t="n">
-        <v>89026012796</v>
+        <v>91846386557</v>
       </c>
       <c r="V31" s="5" t="n">
-        <v>9154494</v>
+        <v>91217802025</v>
       </c>
       <c r="W31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X31" s="5" t="n">
-        <v>3165.12</v>
+        <v>8185.23</v>
       </c>
       <c r="Y31" s="5" t="n">
         <v>12</v>
       </c>
       <c r="Z31" s="5" t="n">
-        <v>379.81</v>
+        <v>982.23</v>
       </c>
       <c r="AA31" s="5" t="inlineStr">
         <is>
@@ -7822,13 +7822,13 @@
         </is>
       </c>
       <c r="AB31" s="6" t="n">
-        <v>45870</v>
+        <v>45886</v>
       </c>
       <c r="AC31" s="6" t="n">
-        <v>45870</v>
+        <v>45886</v>
       </c>
       <c r="AD31" s="5" t="n">
-        <v>379.81</v>
+        <v>982.23</v>
       </c>
       <c r="AE31" s="5" t="inlineStr">
         <is>
@@ -7839,40 +7839,40 @@
         <v>0</v>
       </c>
       <c r="AG31" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH31" s="5" t="inlineStr"/>
       <c r="AI31" s="5" t="inlineStr"/>
       <c r="AJ31" s="5" t="n">
-        <v>964618</v>
+        <v>905448</v>
       </c>
       <c r="AK31" s="5" t="inlineStr"/>
       <c r="AL31" s="6" t="n">
-        <v>45870</v>
+        <v>45886</v>
       </c>
       <c r="AM31" s="5" t="inlineStr"/>
       <c r="AN31" s="6" t="n">
-        <v>45870</v>
+        <v>45886</v>
       </c>
       <c r="AO31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP31" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ31" s="5" t="inlineStr">
         <is>
-          <t>Cirurgia Geral</t>
+          <t>Psiquiatria</t>
         </is>
       </c>
       <c r="AR31" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL - Plano Exemplo</t>
+          <t>EMPRESARIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS31" s="5" t="inlineStr">
         <is>
-          <t>9154494</t>
+          <t>9121780</t>
         </is>
       </c>
       <c r="AT31" s="5" t="b">
@@ -7882,7 +7882,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>PROD-004406</t>
+          <t>PROD-004408</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>4406</v>
+        <v>4408</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -7900,39 +7900,39 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>45886</v>
+        <v>45867</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>901247</v>
+        <v>544859</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>45886</v>
+        <v>45867</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>46251</v>
+        <v>46232</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7966,19 +7966,19 @@
         <v>91846386557</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>91217802025</v>
+        <v>98380962025</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>8185.23</v>
+        <v>403.86</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>982.23</v>
+        <v>72.69</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -7986,13 +7986,13 @@
         </is>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>45886</v>
+        <v>45867</v>
       </c>
       <c r="AC32" s="4" t="n">
-        <v>45886</v>
+        <v>45867</v>
       </c>
       <c r="AD32" s="3" t="n">
-        <v>982.23</v>
+        <v>72.69</v>
       </c>
       <c r="AE32" s="3" t="inlineStr">
         <is>
@@ -8008,21 +8008,21 @@
       <c r="AH32" s="3" t="inlineStr"/>
       <c r="AI32" s="3" t="inlineStr"/>
       <c r="AJ32" s="3" t="n">
-        <v>905448</v>
+        <v>336130</v>
       </c>
       <c r="AK32" s="3" t="inlineStr"/>
       <c r="AL32" s="4" t="n">
-        <v>45886</v>
+        <v>45867</v>
       </c>
       <c r="AM32" s="3" t="inlineStr"/>
       <c r="AN32" s="4" t="n">
-        <v>45886</v>
+        <v>45867</v>
       </c>
       <c r="AO32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP32" s="3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
@@ -8031,12 +8031,12 @@
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL - Plano Exemplo</t>
+          <t>RESIDENCIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>9121780</t>
+          <t>9838096</t>
         </is>
       </c>
       <c r="AT32" s="3" t="b">
@@ -8046,7 +8046,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>PROD-004408</t>
+          <t>PROD-004460</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -8055,48 +8055,48 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>4408</v>
+        <v>4460</v>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>24051477053</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="I33" s="6" t="n">
-        <v>45867</v>
+        <v>45897</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>544859</v>
+        <v>545643</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>45867</v>
+        <v>45897</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>46232</v>
+        <v>46262</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
@@ -8112,7 +8112,7 @@
       <c r="P33" s="5" t="inlineStr"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr">
@@ -8123,26 +8123,26 @@
       <c r="S33" s="5" t="inlineStr"/>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t>Helena Gomes</t>
+          <t>Júlia Rodrigues</t>
         </is>
       </c>
       <c r="U33" s="5" t="n">
-        <v>91846386557</v>
+        <v>24051477053</v>
       </c>
       <c r="V33" s="5" t="n">
-        <v>98380962025</v>
+        <v>1317536</v>
       </c>
       <c r="W33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X33" s="5" t="n">
-        <v>403.86</v>
+        <v>3443.15</v>
       </c>
       <c r="Y33" s="5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Z33" s="5" t="n">
-        <v>72.69</v>
+        <v>413.18</v>
       </c>
       <c r="AA33" s="5" t="inlineStr">
         <is>
@@ -8150,13 +8150,13 @@
         </is>
       </c>
       <c r="AB33" s="6" t="n">
-        <v>45867</v>
+        <v>45897</v>
       </c>
       <c r="AC33" s="6" t="n">
-        <v>45867</v>
+        <v>45897</v>
       </c>
       <c r="AD33" s="5" t="n">
-        <v>72.69</v>
+        <v>413.18</v>
       </c>
       <c r="AE33" s="5" t="inlineStr">
         <is>
@@ -8167,40 +8167,40 @@
         <v>0</v>
       </c>
       <c r="AG33" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH33" s="5" t="inlineStr"/>
       <c r="AI33" s="5" t="inlineStr"/>
       <c r="AJ33" s="5" t="n">
-        <v>336130</v>
+        <v>395720</v>
       </c>
       <c r="AK33" s="5" t="inlineStr"/>
       <c r="AL33" s="6" t="n">
-        <v>45867</v>
+        <v>45897</v>
       </c>
       <c r="AM33" s="5" t="inlineStr"/>
       <c r="AN33" s="6" t="n">
-        <v>45867</v>
+        <v>45897</v>
       </c>
       <c r="AO33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP33" s="5" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AQ33" s="5" t="inlineStr">
         <is>
-          <t>Psiquiatria</t>
+          <t>Clínica Médica</t>
         </is>
       </c>
       <c r="AR33" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL - Plano Exemplo</t>
+          <t>EQUIPAMENTOS - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS33" s="5" t="inlineStr">
         <is>
-          <t>9838096</t>
+          <t>1317536</t>
         </is>
       </c>
       <c r="AT33" s="5" t="b">
@@ -8210,7 +8210,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>PROD-004460</t>
+          <t>PROD-004701</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -8219,48 +8219,48 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>4460</v>
+        <v>4701</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>24051477053</t>
+          <t>26011939103</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>45897</v>
+        <v>45884</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>545643</v>
+        <v>505363</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>45897</v>
+        <v>45884</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>46262</v>
+        <v>46249</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -8287,26 +8287,26 @@
       <c r="S34" s="3" t="inlineStr"/>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>Júlia Rodrigues</t>
+          <t>Eduardo Oliveira</t>
         </is>
       </c>
       <c r="U34" s="3" t="n">
-        <v>24051477053</v>
+        <v>26011939103</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>1317536</v>
+        <v>9693054</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>3443.15</v>
+        <v>2231.56</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>413.18</v>
+        <v>669.47</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -8314,13 +8314,13 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>45897</v>
+        <v>45884</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>45897</v>
+        <v>45884</v>
       </c>
       <c r="AD34" s="3" t="n">
-        <v>413.18</v>
+        <v>669.47</v>
       </c>
       <c r="AE34" s="3" t="inlineStr">
         <is>
@@ -8336,35 +8336,35 @@
       <c r="AH34" s="3" t="inlineStr"/>
       <c r="AI34" s="3" t="inlineStr"/>
       <c r="AJ34" s="3" t="n">
-        <v>395720</v>
+        <v>793543</v>
       </c>
       <c r="AK34" s="3" t="inlineStr"/>
       <c r="AL34" s="4" t="n">
-        <v>45897</v>
+        <v>45884</v>
       </c>
       <c r="AM34" s="3" t="inlineStr"/>
       <c r="AN34" s="4" t="n">
-        <v>45897</v>
+        <v>45884</v>
       </c>
       <c r="AO34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP34" s="3" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>Clínica Médica</t>
+          <t>Pediatria</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>1317536</t>
+          <t>9693054</t>
         </is>
       </c>
       <c r="AT34" s="3" t="b">
@@ -8374,7 +8374,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PROD-004701</t>
+          <t>PROD-004731</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -8383,16 +8383,16 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>4701</v>
+        <v>4731</v>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>26011939103</t>
+          <t>15313636317</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -8411,20 +8411,20 @@
         </is>
       </c>
       <c r="I35" s="6" t="n">
-        <v>45884</v>
+        <v>45915</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>505363</v>
+        <v>423913</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>45884</v>
+        <v>45915</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>46249</v>
+        <v>46280</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr">
@@ -8440,7 +8440,7 @@
       <c r="P35" s="5" t="inlineStr"/>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr">
@@ -8451,26 +8451,26 @@
       <c r="S35" s="5" t="inlineStr"/>
       <c r="T35" s="5" t="inlineStr">
         <is>
-          <t>Eduardo Oliveira</t>
+          <t>Fernanda Martins</t>
         </is>
       </c>
       <c r="U35" s="5" t="n">
-        <v>26011939103</v>
+        <v>15313636317</v>
       </c>
       <c r="V35" s="5" t="n">
-        <v>9693054</v>
+        <v>3262616</v>
       </c>
       <c r="W35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X35" s="5" t="n">
-        <v>2231.56</v>
+        <v>3908.5</v>
       </c>
       <c r="Y35" s="5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Z35" s="5" t="n">
-        <v>669.47</v>
+        <v>1637.11</v>
       </c>
       <c r="AA35" s="5" t="inlineStr">
         <is>
@@ -8478,13 +8478,13 @@
         </is>
       </c>
       <c r="AB35" s="6" t="n">
-        <v>45884</v>
+        <v>45915</v>
       </c>
       <c r="AC35" s="6" t="n">
-        <v>45884</v>
+        <v>45915</v>
       </c>
       <c r="AD35" s="5" t="n">
-        <v>669.47</v>
+        <v>1637.11</v>
       </c>
       <c r="AE35" s="5" t="inlineStr">
         <is>
@@ -8500,25 +8500,25 @@
       <c r="AH35" s="5" t="inlineStr"/>
       <c r="AI35" s="5" t="inlineStr"/>
       <c r="AJ35" s="5" t="n">
-        <v>793543</v>
+        <v>133581</v>
       </c>
       <c r="AK35" s="5" t="inlineStr"/>
       <c r="AL35" s="6" t="n">
-        <v>45884</v>
+        <v>45915</v>
       </c>
       <c r="AM35" s="5" t="inlineStr"/>
       <c r="AN35" s="6" t="n">
-        <v>45884</v>
+        <v>45915</v>
       </c>
       <c r="AO35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP35" s="5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AQ35" s="5" t="inlineStr">
         <is>
-          <t>Pediatria</t>
+          <t>Clínica Médica</t>
         </is>
       </c>
       <c r="AR35" s="5" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AS35" s="5" t="inlineStr">
         <is>
-          <t>9693054</t>
+          <t>3262616</t>
         </is>
       </c>
       <c r="AT35" s="5" t="b">
@@ -8538,7 +8538,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>PROD-004731</t>
+          <t>PROD-004748</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8547,11 +8547,11 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>4731</v>
+        <v>4748</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>15313636317</t>
+          <t>87258874495</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -8575,16 +8575,16 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>45915</v>
+        <v>45900</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>423913</v>
+        <v>307099</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>45915</v>
+        <v>45900</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>46280</v>
+        <v>46265</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -8615,26 +8615,26 @@
       <c r="S36" s="3" t="inlineStr"/>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>Fernanda Martins</t>
+          <t>Mariana Oliveira</t>
         </is>
       </c>
       <c r="U36" s="3" t="n">
-        <v>15313636317</v>
+        <v>87258874495</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>3262616</v>
+        <v>8679757</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>3908.5</v>
+        <v>4433.94</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>20</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1637.11</v>
+        <v>886.79</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -8642,13 +8642,13 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>45915</v>
+        <v>45900</v>
       </c>
       <c r="AC36" s="4" t="n">
-        <v>45915</v>
+        <v>45900</v>
       </c>
       <c r="AD36" s="3" t="n">
-        <v>1637.11</v>
+        <v>886.79</v>
       </c>
       <c r="AE36" s="3" t="inlineStr">
         <is>
@@ -8664,25 +8664,25 @@
       <c r="AH36" s="3" t="inlineStr"/>
       <c r="AI36" s="3" t="inlineStr"/>
       <c r="AJ36" s="3" t="n">
-        <v>133581</v>
+        <v>819866</v>
       </c>
       <c r="AK36" s="3" t="inlineStr"/>
       <c r="AL36" s="4" t="n">
-        <v>45915</v>
+        <v>45900</v>
       </c>
       <c r="AM36" s="3" t="inlineStr"/>
       <c r="AN36" s="4" t="n">
-        <v>45915</v>
+        <v>45900</v>
       </c>
       <c r="AO36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP36" s="3" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>Clínica Médica</t>
+          <t>Cardiologia</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>3262616</t>
+          <t>8679757</t>
         </is>
       </c>
       <c r="AT36" s="3" t="b">
@@ -8702,7 +8702,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PROD-004748</t>
+          <t>PROD-004756</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -8711,11 +8711,11 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>4748</v>
+        <v>4756</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>87258874495</t>
+          <t>71657262849</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -8739,16 +8739,16 @@
         </is>
       </c>
       <c r="I37" s="6" t="n">
-        <v>45900</v>
+        <v>45904</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>307099</v>
+        <v>874662</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>45900</v>
+        <v>45904</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
@@ -8779,26 +8779,26 @@
       <c r="S37" s="5" t="inlineStr"/>
       <c r="T37" s="5" t="inlineStr">
         <is>
-          <t>Mariana Oliveira</t>
+          <t>Daniel Martins</t>
         </is>
       </c>
       <c r="U37" s="5" t="n">
-        <v>87258874495</v>
+        <v>71657262849</v>
       </c>
       <c r="V37" s="5" t="n">
-        <v>8679757</v>
+        <v>9280290</v>
       </c>
       <c r="W37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X37" s="5" t="n">
-        <v>4433.94</v>
+        <v>3843.36</v>
       </c>
       <c r="Y37" s="5" t="n">
         <v>20</v>
       </c>
       <c r="Z37" s="5" t="n">
-        <v>886.79</v>
+        <v>5041.73</v>
       </c>
       <c r="AA37" s="5" t="inlineStr">
         <is>
@@ -8806,13 +8806,13 @@
         </is>
       </c>
       <c r="AB37" s="6" t="n">
-        <v>45900</v>
+        <v>45904</v>
       </c>
       <c r="AC37" s="6" t="n">
-        <v>45900</v>
+        <v>45904</v>
       </c>
       <c r="AD37" s="5" t="n">
-        <v>886.79</v>
+        <v>5041.73</v>
       </c>
       <c r="AE37" s="5" t="inlineStr">
         <is>
@@ -8828,25 +8828,25 @@
       <c r="AH37" s="5" t="inlineStr"/>
       <c r="AI37" s="5" t="inlineStr"/>
       <c r="AJ37" s="5" t="n">
-        <v>819866</v>
+        <v>431798</v>
       </c>
       <c r="AK37" s="5" t="inlineStr"/>
       <c r="AL37" s="6" t="n">
-        <v>45900</v>
+        <v>45904</v>
       </c>
       <c r="AM37" s="5" t="inlineStr"/>
       <c r="AN37" s="6" t="n">
-        <v>45900</v>
+        <v>45904</v>
       </c>
       <c r="AO37" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP37" s="5" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AQ37" s="5" t="inlineStr">
         <is>
-          <t>Cardiologia</t>
+          <t>Otorrinolaringologia</t>
         </is>
       </c>
       <c r="AR37" s="5" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="AS37" s="5" t="inlineStr">
         <is>
-          <t>8679757</t>
+          <t>9280290</t>
         </is>
       </c>
       <c r="AT37" s="5" t="b">
@@ -8866,7 +8866,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>PROD-004756</t>
+          <t>PROD-004766</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8875,11 +8875,11 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>4756</v>
+        <v>4766</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>71657262849</t>
+          <t>62244472126</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -8903,16 +8903,16 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>45904</v>
+        <v>45900</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>874662</v>
+        <v>903738</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>45904</v>
+        <v>45900</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -8943,26 +8943,26 @@
       <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>Daniel Martins</t>
+          <t>Rafaela Lima</t>
         </is>
       </c>
       <c r="U38" s="3" t="n">
-        <v>71657262849</v>
+        <v>62244472126</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>9280290</v>
+        <v>8882503</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>3843.36</v>
+        <v>3848.65</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>20</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>5041.73</v>
+        <v>769.73</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -8970,13 +8970,13 @@
         </is>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>45904</v>
+        <v>45900</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>45904</v>
+        <v>45900</v>
       </c>
       <c r="AD38" s="3" t="n">
-        <v>5041.73</v>
+        <v>769.73</v>
       </c>
       <c r="AE38" s="3" t="inlineStr">
         <is>
@@ -8992,25 +8992,25 @@
       <c r="AH38" s="3" t="inlineStr"/>
       <c r="AI38" s="3" t="inlineStr"/>
       <c r="AJ38" s="3" t="n">
-        <v>431798</v>
+        <v>912454</v>
       </c>
       <c r="AK38" s="3" t="inlineStr"/>
       <c r="AL38" s="4" t="n">
-        <v>45904</v>
+        <v>45900</v>
       </c>
       <c r="AM38" s="3" t="inlineStr"/>
       <c r="AN38" s="4" t="n">
-        <v>45904</v>
+        <v>45900</v>
       </c>
       <c r="AO38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP38" s="3" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>Otorrinolaringologia</t>
+          <t>Cirurgia Geral</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>9280290</t>
+          <t>8882503</t>
         </is>
       </c>
       <c r="AT38" s="3" t="b">
@@ -9030,7 +9030,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>PROD-004766</t>
+          <t>PROD-004768</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -9039,11 +9039,11 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>4766</v>
+        <v>4768</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>62244472126</t>
+          <t>62003424420</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -9067,16 +9067,16 @@
         </is>
       </c>
       <c r="I39" s="6" t="n">
-        <v>45900</v>
+        <v>45889</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>903738</v>
+        <v>467781</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>45900</v>
+        <v>45889</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>46265</v>
+        <v>46254</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
@@ -9107,26 +9107,26 @@
       <c r="S39" s="5" t="inlineStr"/>
       <c r="T39" s="5" t="inlineStr">
         <is>
-          <t>Rafaela Lima</t>
+          <t>Fernanda Costa</t>
         </is>
       </c>
       <c r="U39" s="5" t="n">
-        <v>62244472126</v>
+        <v>62003424420</v>
       </c>
       <c r="V39" s="5" t="n">
-        <v>8882503</v>
+        <v>4835183</v>
       </c>
       <c r="W39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X39" s="5" t="n">
-        <v>3848.65</v>
+        <v>4243.38</v>
       </c>
       <c r="Y39" s="5" t="n">
         <v>20</v>
       </c>
       <c r="Z39" s="5" t="n">
-        <v>769.73</v>
+        <v>848.6799999999999</v>
       </c>
       <c r="AA39" s="5" t="inlineStr">
         <is>
@@ -9134,13 +9134,13 @@
         </is>
       </c>
       <c r="AB39" s="6" t="n">
-        <v>45900</v>
+        <v>45889</v>
       </c>
       <c r="AC39" s="6" t="n">
-        <v>45900</v>
+        <v>45889</v>
       </c>
       <c r="AD39" s="5" t="n">
-        <v>769.73</v>
+        <v>848.6799999999999</v>
       </c>
       <c r="AE39" s="5" t="inlineStr">
         <is>
@@ -9151,30 +9151,30 @@
         <v>0</v>
       </c>
       <c r="AG39" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH39" s="5" t="inlineStr"/>
       <c r="AI39" s="5" t="inlineStr"/>
       <c r="AJ39" s="5" t="n">
-        <v>912454</v>
+        <v>377347</v>
       </c>
       <c r="AK39" s="5" t="inlineStr"/>
       <c r="AL39" s="6" t="n">
-        <v>45900</v>
+        <v>45889</v>
       </c>
       <c r="AM39" s="5" t="inlineStr"/>
       <c r="AN39" s="6" t="n">
-        <v>45900</v>
+        <v>45889</v>
       </c>
       <c r="AO39" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP39" s="5" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="AQ39" s="5" t="inlineStr">
         <is>
-          <t>Cirurgia Geral</t>
+          <t>Anestesiologia</t>
         </is>
       </c>
       <c r="AR39" s="5" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="AS39" s="5" t="inlineStr">
         <is>
-          <t>8882503</t>
+          <t>4835183</t>
         </is>
       </c>
       <c r="AT39" s="5" t="b">
@@ -9194,7 +9194,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>PROD-004768</t>
+          <t>PROD-004770</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9203,11 +9203,11 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4768</v>
+        <v>4770</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>62003424420</t>
+          <t>45547813767</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -9231,16 +9231,16 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>45889</v>
+        <v>45920</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>467781</v>
+        <v>534534</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>45889</v>
+        <v>45920</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>46254</v>
+        <v>46285</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -9271,26 +9271,26 @@
       <c r="S40" s="3" t="inlineStr"/>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>Fernanda Costa</t>
+          <t>Ana Oliveira</t>
         </is>
       </c>
       <c r="U40" s="3" t="n">
-        <v>62003424420</v>
+        <v>45547813767</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>4835183</v>
+        <v>9625375</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>4243.38</v>
+        <v>4191.78</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>20</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>848.6799999999999</v>
+        <v>838.36</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -9298,13 +9298,13 @@
         </is>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>45889</v>
+        <v>45920</v>
       </c>
       <c r="AC40" s="4" t="n">
-        <v>45889</v>
+        <v>45920</v>
       </c>
       <c r="AD40" s="3" t="n">
-        <v>848.6799999999999</v>
+        <v>838.36</v>
       </c>
       <c r="AE40" s="3" t="inlineStr">
         <is>
@@ -9315,30 +9315,30 @@
         <v>0</v>
       </c>
       <c r="AG40" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AH40" s="3" t="inlineStr"/>
       <c r="AI40" s="3" t="inlineStr"/>
       <c r="AJ40" s="3" t="n">
-        <v>377347</v>
+        <v>909681</v>
       </c>
       <c r="AK40" s="3" t="inlineStr"/>
       <c r="AL40" s="4" t="n">
-        <v>45889</v>
+        <v>45920</v>
       </c>
       <c r="AM40" s="3" t="inlineStr"/>
       <c r="AN40" s="4" t="n">
-        <v>45889</v>
+        <v>45920</v>
       </c>
       <c r="AO40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP40" s="3" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>Anestesiologia</t>
+          <t>Psiquiatria</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>4835183</t>
+          <t>9625375</t>
         </is>
       </c>
       <c r="AT40" s="3" t="b">

--- a/outputs/comercial/auditoria/Agenda_Renovacoes.xlsx
+++ b/outputs/comercial/auditoria/Agenda_Renovacoes.xlsx
@@ -11,8 +11,8 @@
     <sheet name="2_Lastro" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1_Agregado'!$A$1:$O$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_Lastro'!$A$1:$AT$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1_Agregado'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_Lastro'!$A$1:$AT$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>68011280598</t>
+          <t>22535841438</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -605,10 +605,10 @@
         </is>
       </c>
       <c r="H2" s="3" t="n">
-        <v>5218.51</v>
+        <v>10437.02</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>782.78</v>
+        <v>1565.56</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>1</v>
@@ -620,19 +620,19 @@
         <v>1</v>
       </c>
       <c r="M2" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O2" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>76617711592</t>
+          <t>87719065940</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -675,19 +675,19 @@
         <v>1</v>
       </c>
       <c r="M3" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O3" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>25534192832</t>
+          <t>18102203173</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -730,19 +730,19 @@
         <v>1</v>
       </c>
       <c r="M4" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O4" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>08240433504</t>
+          <t>67883171210</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -785,19 +785,19 @@
         <v>1</v>
       </c>
       <c r="M5" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O5" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>15890429025</t>
+          <t>22820055778</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -840,19 +840,19 @@
         <v>1</v>
       </c>
       <c r="M6" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O6" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>63942788165</t>
+          <t>31752071678</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -886,7 +886,7 @@
         <v>1292.2</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="5" t="b">
         <v>1</v>
@@ -907,7 +907,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>85642059304</t>
+          <t>60466183982</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -950,19 +950,19 @@
         <v>1</v>
       </c>
       <c r="M8" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O8" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>13858542493</t>
+          <t>01372151070</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1005,19 +1005,19 @@
         <v>1</v>
       </c>
       <c r="M9" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O9" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>56704310385</t>
+          <t>26368970283</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1048,7 +1048,7 @@
         <v>323.15</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>96.94</v>
+        <v>389.68</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>1</v>
@@ -1060,19 +1060,19 @@
         <v>1</v>
       </c>
       <c r="M10" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O10" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>04341651827</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>403.86</v>
+        <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>72.69</v>
@@ -1115,19 +1115,19 @@
         <v>1</v>
       </c>
       <c r="M11" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O11" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>89026012796</t>
+          <t>32677360260</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>58514936899</t>
+          <t>87258874495</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1213,7 +1213,7 @@
         <v>7580.02</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>4323.47</v>
+        <v>2274.01</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>3</v>
@@ -1225,19 +1225,19 @@
         <v>1</v>
       </c>
       <c r="M13" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O13" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>28699041379</t>
+          <t>37693898331</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1280,19 +1280,19 @@
         <v>1</v>
       </c>
       <c r="M14" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O14" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>47284639208</t>
+          <t>42843479552</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1323,7 +1323,7 @@
         <v>7846.91</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>1683.32</v>
+        <v>941.63</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>3</v>
@@ -1335,19 +1335,19 @@
         <v>1</v>
       </c>
       <c r="M15" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O15" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>95701543039</t>
+          <t>37562890028</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1390,24 +1390,24 @@
         <v>1</v>
       </c>
       <c r="M16" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O16" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>12499856984</t>
+          <t>56475705120</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>5693.24</v>
+        <v>8370.52</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>853.99</v>
+        <v>1506.69</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>3</v>
@@ -1457,12 +1457,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>19148564679</t>
+          <t>88615335554</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>8370.52</v>
+        <v>5693.24</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1506.69</v>
+        <v>7742.39</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3</v>
@@ -1500,19 +1500,19 @@
         <v>1</v>
       </c>
       <c r="M18" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O18" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>26011939103</t>
+          <t>93305172897</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1549,16 +1549,16 @@
         <v>2</v>
       </c>
       <c r="K19" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="5" t="b">
         <v>0</v>
       </c>
       <c r="N19" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="5" t="b">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>04341651827</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1598,7 +1598,7 @@
         <v>8185.23</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>982.23</v>
+        <v>1456.43</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>2</v>
@@ -1610,19 +1610,19 @@
         <v>1</v>
       </c>
       <c r="M20" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O20" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>62003424420</t>
+          <t>55460158517</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
@@ -1650,13 +1650,13 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>4243.38</v>
+        <v>4495.3</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>848.6799999999999</v>
+        <v>899.0599999999999</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" s="5" t="b">
         <v>1</v>
@@ -1677,7 +1677,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>52056647423</t>
+          <t>04556110022</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>3293.99</v>
+        <v>4287.11</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>4973.87</v>
+        <v>857.42</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3</v>
@@ -1732,7 +1732,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>08589944171</t>
+          <t>09859317461</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1742,28 +1742,28 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>45892</v>
+        <v>45891</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>🟢 61 a 90 dias</t>
+          <t>🟡 31 a 60 dias</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>1616.84</v>
+        <v>3293.99</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>404.21</v>
+        <v>494.1</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>3</v>
@@ -1787,27 +1787,27 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>24051477053</t>
+          <t>65094801413</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>45897</v>
+        <v>45892</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>46262</v>
+        <v>46257</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>3443.15</v>
+        <v>1616.84</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>413.18</v>
+        <v>404.21</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K24" s="3" t="b">
         <v>1</v>
@@ -1842,7 +1842,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>37562890028</t>
+          <t>11435190669</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1856,13 +1856,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>45750</v>
+        <v>45893</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>46263</v>
+        <v>46258</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -1870,13 +1870,13 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>6019.52</v>
+        <v>4244.43</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>1447.99</v>
+        <v>848.89</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K25" s="5" t="b">
         <v>1</v>
@@ -1897,27 +1897,27 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>62244472126</t>
+          <t>28685289755</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>45900</v>
+        <v>45897</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>3848.65</v>
+        <v>3443.15</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>769.73</v>
+        <v>413.18</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K26" s="3" t="b">
         <v>1</v>
@@ -1940,19 +1940,19 @@
         <v>1</v>
       </c>
       <c r="M26" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O26" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>87258874495</t>
+          <t>39385258001</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -1966,13 +1966,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>45900</v>
+        <v>45902</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>4433.94</v>
+        <v>8069.86</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>886.79</v>
+        <v>1613.98</v>
       </c>
       <c r="J27" s="5" t="n">
         <v>3</v>
@@ -1995,19 +1995,19 @@
         <v>1</v>
       </c>
       <c r="M27" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O27" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>38657191826</t>
+          <t>77418625652</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2062,7 +2062,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>71657262849</t>
+          <t>08993588916</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2072,17 +2072,17 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>45904</v>
+        <v>45906</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>46269</v>
+        <v>46271</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>3843.36</v>
+        <v>4592.43</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>5041.73</v>
+        <v>688.86</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" s="5" t="b">
         <v>1</v>
@@ -2105,19 +2105,19 @@
         <v>1</v>
       </c>
       <c r="M29" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O29" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>70335211039</t>
+          <t>66978480184</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2127,17 +2127,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>45906</v>
+        <v>45908</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>9184.860000000001</v>
+        <v>3755.46</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1377.72</v>
+        <v>751.09</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="3" t="b">
         <v>1</v>
@@ -2160,19 +2160,19 @@
         <v>1</v>
       </c>
       <c r="M30" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O30" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>42836440892</t>
+          <t>54019380262</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>45911</v>
+        <v>45909</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>5525.39</v>
+        <v>3912.42</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>663.05</v>
+        <v>782.48</v>
       </c>
       <c r="J31" s="5" t="n">
         <v>3</v>
@@ -2227,27 +2227,27 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>74783667428</t>
+          <t>32898614341</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>45912</v>
+        <v>45911</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2742.66</v>
+        <v>5525.39</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>329.12</v>
+        <v>663.05</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K32" s="3" t="b">
         <v>1</v>
@@ -2270,39 +2270,39 @@
         <v>1</v>
       </c>
       <c r="M32" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O32" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>75901751863</t>
+          <t>37124065965</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>45913</v>
+        <v>45912</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
@@ -2310,13 +2310,13 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>6204.82</v>
+        <v>2742.66</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>930.72</v>
+        <v>329.12</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K33" s="5" t="b">
         <v>1</v>
@@ -2337,27 +2337,27 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>15313636317</t>
+          <t>13736785082</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>45915</v>
+        <v>45913</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>46280</v>
+        <v>46278</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3908.5</v>
+        <v>6204.82</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1637.11</v>
+        <v>930.72</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3</v>
@@ -2392,7 +2392,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>51713395962</t>
+          <t>14921643347</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>12502.32</v>
+        <v>5957.01331434156</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>3346.76</v>
+        <v>1993.6</v>
       </c>
       <c r="J35" s="5" t="n">
         <v>3</v>
@@ -2435,39 +2435,39 @@
         <v>1</v>
       </c>
       <c r="M35" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O35" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>78292216995</t>
+          <t>96631931491</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>45917</v>
+        <v>45916</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>4494.66</v>
+        <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>539.36</v>
+        <v>848.27</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>3</v>
@@ -2502,27 +2502,27 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>54868740345</t>
+          <t>20616329451</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>45918</v>
+        <v>45917</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>498.86</v>
+        <v>4137.09</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>74.83</v>
+        <v>827.42</v>
       </c>
       <c r="J37" s="5" t="n">
         <v>3</v>
@@ -2545,39 +2545,39 @@
         <v>1</v>
       </c>
       <c r="M37" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="5" t="b">
         <v>1</v>
       </c>
       <c r="O37" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>45547813767</t>
+          <t>89994043898</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>45920</v>
+        <v>45918</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>46285</v>
+        <v>46283</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>4191.78</v>
+        <v>0</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>838.36</v>
+        <v>74.83</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K38" s="3" t="b">
         <v>1</v>
@@ -2600,72 +2600,127 @@
         <v>1</v>
       </c>
       <c r="M38" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" s="3" t="b">
         <v>1</v>
       </c>
       <c r="O38" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>85368663266</t>
+          <t>81845184894</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
+          <t>ALFA</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>AUTOMÓVEL</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>45918</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>🟢 61 a 90 dias</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>4292.44</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>858.49</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>57437489691</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
           <t>BETA</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>AUTOMÓVEL</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D40" s="4" t="n">
         <v>45921</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E40" s="4" t="n">
         <v>46286</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F40" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>🟢 61 a 90 dias</t>
         </is>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H40" s="3" t="n">
         <v>4188.14</v>
       </c>
-      <c r="I39" s="5" t="n">
-        <v>1407.64</v>
-      </c>
-      <c r="J39" s="5" t="n">
+      <c r="I40" s="3" t="n">
+        <v>628.22</v>
+      </c>
+      <c r="J40" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="O39" s="5" t="b">
+      <c r="K40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" s="3" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
+  <autoFilter ref="A1:O40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2676,7 +2731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT42"/>
+  <dimension ref="A1:AT43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2698,14 +2753,14 @@
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="23" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="23" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="37" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
     <col width="21" customWidth="1" min="28" max="28"/>
     <col width="21" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
@@ -2962,7 +3017,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>PROD-000249</t>
+          <t>PROD-000176</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2971,48 +3026,48 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>249</v>
+        <v>176</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>78292216995</t>
+          <t>08993588916</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>45917</v>
+        <v>45906</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>543478</v>
+        <v>336446</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>45917</v>
+        <v>45906</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>46282</v>
+        <v>46271</v>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -3039,40 +3094,40 @@
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>Daniel Almeida</t>
+          <t>Bruno Lima</t>
         </is>
       </c>
       <c r="U2" s="3" t="n">
-        <v>78292216995</v>
+        <v>8993588916</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>27853782025</v>
+        <v>1430716</v>
       </c>
       <c r="W2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>4494.66</v>
+        <v>4592.43</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>539.36</v>
+        <v>688.86</v>
       </c>
       <c r="AA2" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>45917</v>
+        <v>45906</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>45917</v>
+        <v>45906</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>539.36</v>
+        <v>688.86</v>
       </c>
       <c r="AE2" s="3" t="inlineStr">
         <is>
@@ -3083,40 +3138,40 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH2" s="3" t="inlineStr"/>
       <c r="AI2" s="3" t="inlineStr"/>
       <c r="AJ2" s="3" t="n">
-        <v>615710</v>
+        <v>234921</v>
       </c>
       <c r="AK2" s="3" t="inlineStr"/>
       <c r="AL2" s="4" t="n">
-        <v>45917</v>
+        <v>45906</v>
       </c>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="4" t="n">
-        <v>45917</v>
+        <v>45906</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr">
         <is>
-          <t>Cardiologia</t>
+          <t>Psiquiatria</t>
         </is>
       </c>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL - Plano Exemplo</t>
+          <t>EQUIPAMENTOS - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
         <is>
-          <t>2785378</t>
+          <t>1430716</t>
         </is>
       </c>
       <c r="AT2" s="3" t="b">
@@ -3126,7 +3181,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>PROD-000476</t>
+          <t>PROD-000212</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -3135,11 +3190,11 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>476</v>
+        <v>212</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>70335211039</t>
+          <t>32898614341</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -3149,30 +3204,30 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I3" s="6" t="n">
-        <v>45906</v>
+        <v>45911</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>336446</v>
+        <v>928332</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>45906</v>
+        <v>45911</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>46271</v>
+        <v>46276</v>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
@@ -3203,40 +3258,40 @@
       <c r="S3" s="5" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>Daniel Barbosa</t>
+          <t>Igor Rodrigues</t>
         </is>
       </c>
       <c r="U3" s="5" t="n">
-        <v>70335211039</v>
+        <v>32898614341</v>
       </c>
       <c r="V3" s="5" t="n">
-        <v>1430716</v>
+        <v>88917292025</v>
       </c>
       <c r="W3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>4592.43</v>
+        <v>5525.39</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>688.86</v>
+        <v>663.05</v>
       </c>
       <c r="AA3" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="AB3" s="6" t="n">
-        <v>45906</v>
+        <v>45911</v>
       </c>
       <c r="AC3" s="6" t="n">
-        <v>45906</v>
+        <v>45911</v>
       </c>
       <c r="AD3" s="5" t="n">
-        <v>688.86</v>
+        <v>663.05</v>
       </c>
       <c r="AE3" s="5" t="inlineStr">
         <is>
@@ -3247,40 +3302,40 @@
         <v>0</v>
       </c>
       <c r="AG3" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AH3" s="5" t="inlineStr"/>
       <c r="AI3" s="5" t="inlineStr"/>
       <c r="AJ3" s="5" t="n">
-        <v>234921</v>
+        <v>861695</v>
       </c>
       <c r="AK3" s="5" t="inlineStr"/>
       <c r="AL3" s="6" t="n">
-        <v>45906</v>
+        <v>45911</v>
       </c>
       <c r="AM3" s="5" t="inlineStr"/>
       <c r="AN3" s="6" t="n">
-        <v>45906</v>
+        <v>45911</v>
       </c>
       <c r="AO3" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP3" s="5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ3" s="5" t="inlineStr">
         <is>
-          <t>Otorrinolaringologia</t>
+          <t>Radiologia</t>
         </is>
       </c>
       <c r="AR3" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS3" s="5" t="inlineStr">
         <is>
-          <t>1430716</t>
+          <t>8891729</t>
         </is>
       </c>
       <c r="AT3" s="5" t="b">
@@ -3290,7 +3345,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>PROD-000512</t>
+          <t>PROD-000491</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3299,48 +3354,48 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>512</v>
+        <v>491</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>42836440892</t>
+          <t>37562890028</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>45911</v>
+        <v>45881</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>928332</v>
+        <v>380622</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>45911</v>
+        <v>45881</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>46276</v>
+        <v>46246</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -3367,40 +3422,40 @@
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Daniel Rodrigues</t>
+          <t>Eduardo Martins</t>
         </is>
       </c>
       <c r="U4" s="3" t="n">
-        <v>42836440892</v>
+        <v>37562890028</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>88917292025</v>
+        <v>1083492</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>5525.39</v>
+        <v>4025.31</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>663.05</v>
+        <v>724.5599999999999</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>45911</v>
+        <v>45881</v>
       </c>
       <c r="AC4" s="4" t="n">
-        <v>45911</v>
+        <v>45881</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>663.05</v>
+        <v>724.5599999999999</v>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
@@ -3416,35 +3471,35 @@
       <c r="AH4" s="3" t="inlineStr"/>
       <c r="AI4" s="3" t="inlineStr"/>
       <c r="AJ4" s="3" t="n">
-        <v>861695</v>
+        <v>550257</v>
       </c>
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" s="4" t="n">
-        <v>45911</v>
+        <v>45881</v>
       </c>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="4" t="n">
-        <v>45911</v>
+        <v>45881</v>
       </c>
       <c r="AO4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP4" s="3" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>Urologia</t>
+          <t>Otorrinolaringologia</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL - Plano Exemplo</t>
+          <t>EQUIPAMENTOS - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>8891729</t>
+          <t>1083492</t>
         </is>
       </c>
       <c r="AT4" s="3" t="b">
@@ -3454,7 +3509,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>PROD-000791</t>
+          <t>PROD-000593</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -3463,48 +3518,48 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>791</v>
+        <v>593</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>95701543039</t>
+          <t>56475705120</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>45881</v>
+        <v>45883</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>380622</v>
+        <v>797203</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>45881</v>
+        <v>45883</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -3531,40 +3586,40 @@
       <c r="S5" s="5" t="inlineStr"/>
       <c r="T5" s="5" t="inlineStr">
         <is>
-          <t>Bruno Araújo</t>
+          <t>Daniel Barbosa</t>
         </is>
       </c>
       <c r="U5" s="5" t="n">
-        <v>95701543039</v>
+        <v>56475705120</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>1083492</v>
+        <v>37637442025</v>
       </c>
       <c r="W5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>4025.31</v>
+        <v>8370.52</v>
       </c>
       <c r="Y5" s="5" t="n">
         <v>18</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>724.5599999999999</v>
+        <v>1506.69</v>
       </c>
       <c r="AA5" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="AB5" s="6" t="n">
-        <v>45881</v>
+        <v>45883</v>
       </c>
       <c r="AC5" s="6" t="n">
-        <v>45881</v>
+        <v>45883</v>
       </c>
       <c r="AD5" s="5" t="n">
-        <v>724.5599999999999</v>
+        <v>1506.69</v>
       </c>
       <c r="AE5" s="5" t="inlineStr">
         <is>
@@ -3575,40 +3630,40 @@
         <v>0</v>
       </c>
       <c r="AG5" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH5" s="5" t="inlineStr"/>
       <c r="AI5" s="5" t="inlineStr"/>
       <c r="AJ5" s="5" t="n">
-        <v>550257</v>
+        <v>770623</v>
       </c>
       <c r="AK5" s="5" t="inlineStr"/>
       <c r="AL5" s="6" t="n">
-        <v>45881</v>
+        <v>45883</v>
       </c>
       <c r="AM5" s="5" t="inlineStr"/>
       <c r="AN5" s="6" t="n">
-        <v>45881</v>
+        <v>45883</v>
       </c>
       <c r="AO5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" s="5" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AQ5" s="5" t="inlineStr">
         <is>
-          <t>Neurologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="AR5" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS - Plano Exemplo</t>
+          <t>RESIDENCIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS5" s="5" t="inlineStr">
         <is>
-          <t>1083492</t>
+          <t>3763744</t>
         </is>
       </c>
       <c r="AT5" s="5" t="b">
@@ -3618,7 +3673,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>PROD-000893</t>
+          <t>PROD-000972</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3627,48 +3682,48 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>893</v>
+        <v>972</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>19148564679</t>
+          <t>37124065965</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>45883</v>
+        <v>45912</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>797203</v>
+        <v>568031</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>45883</v>
+        <v>45912</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>46248</v>
+        <v>46277</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -3684,7 +3739,7 @@
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -3695,40 +3750,40 @@
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Helena Pereira</t>
+          <t>Nelson Lima</t>
         </is>
       </c>
       <c r="U6" s="3" t="n">
-        <v>19148564679</v>
+        <v>37124065965</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>37637442025</v>
+        <v>3081670</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>8370.52</v>
+        <v>2742.66</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1506.69</v>
+        <v>329.12</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>45883</v>
+        <v>45912</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>45883</v>
+        <v>45912</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>1506.69</v>
+        <v>329.12</v>
       </c>
       <c r="AE6" s="3" t="inlineStr">
         <is>
@@ -3739,40 +3794,40 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AH6" s="3" t="inlineStr"/>
       <c r="AI6" s="3" t="inlineStr"/>
       <c r="AJ6" s="3" t="n">
-        <v>770623</v>
+        <v>662533</v>
       </c>
       <c r="AK6" s="3" t="inlineStr"/>
       <c r="AL6" s="4" t="n">
-        <v>45883</v>
+        <v>45912</v>
       </c>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="4" t="n">
-        <v>45883</v>
+        <v>45912</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP6" s="3" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>Endocrinologia</t>
+          <t>Cirurgia Geral</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL - Plano Exemplo</t>
+          <t>EMPRESARIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>3763744</t>
+          <t>3081670</t>
         </is>
       </c>
       <c r="AT6" s="3" t="b">
@@ -3782,7 +3837,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>PROD-001272</t>
+          <t>PROD-001024</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -3791,16 +3846,16 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1272</v>
+        <v>1024</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>74783667428</t>
+          <t>87258874495</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -3810,7 +3865,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -3819,20 +3874,20 @@
         </is>
       </c>
       <c r="I7" s="6" t="n">
-        <v>45912</v>
+        <v>45872</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>568031</v>
+        <v>468089</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>45912</v>
+        <v>45872</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>46277</v>
+        <v>46237</v>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>ÉPSI</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
@@ -3848,7 +3903,7 @@
       <c r="P7" s="5" t="inlineStr"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
@@ -3859,40 +3914,40 @@
       <c r="S7" s="5" t="inlineStr"/>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>Carla Souza</t>
+          <t>Júlia Martins</t>
         </is>
       </c>
       <c r="U7" s="5" t="n">
-        <v>74783667428</v>
+        <v>87258874495</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>3081670</v>
+        <v>7171594</v>
       </c>
       <c r="W7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>2742.66</v>
+        <v>7580.02</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>329.12</v>
+        <v>2274.01</v>
       </c>
       <c r="AA7" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="AB7" s="6" t="n">
-        <v>45912</v>
+        <v>45872</v>
       </c>
       <c r="AC7" s="6" t="n">
-        <v>45912</v>
+        <v>45872</v>
       </c>
       <c r="AD7" s="5" t="n">
-        <v>329.12</v>
+        <v>2274.01</v>
       </c>
       <c r="AE7" s="5" t="inlineStr">
         <is>
@@ -3908,25 +3963,25 @@
       <c r="AH7" s="5" t="inlineStr"/>
       <c r="AI7" s="5" t="inlineStr"/>
       <c r="AJ7" s="5" t="n">
-        <v>662533</v>
+        <v>560553</v>
       </c>
       <c r="AK7" s="5" t="inlineStr"/>
       <c r="AL7" s="6" t="n">
-        <v>45912</v>
+        <v>45872</v>
       </c>
       <c r="AM7" s="5" t="inlineStr"/>
       <c r="AN7" s="6" t="n">
-        <v>45912</v>
+        <v>45872</v>
       </c>
       <c r="AO7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP7" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AQ7" s="5" t="inlineStr">
         <is>
-          <t>Dermatologia</t>
+          <t>Clínica Médica</t>
         </is>
       </c>
       <c r="AR7" s="5" t="inlineStr">
@@ -3936,7 +3991,7 @@
       </c>
       <c r="AS7" s="5" t="inlineStr">
         <is>
-          <t>3081670</t>
+          <t>7171594</t>
         </is>
       </c>
       <c r="AT7" s="5" t="b">
@@ -3946,7 +4001,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>PROD-001324</t>
+          <t>PROD-001137</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3955,48 +4010,48 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1324</v>
+        <v>1137</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>58514936899</t>
+          <t>14921643347</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>45872</v>
+        <v>45916</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>468089</v>
+        <v>538732</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>45872</v>
+        <v>45916</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>46237</v>
+        <v>46281</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>ÉPSI</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -4023,40 +4078,40 @@
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Sérgio Pereira</t>
+          <t>Bruno Lima</t>
         </is>
       </c>
       <c r="U8" s="3" t="n">
-        <v>58514936899</v>
+        <v>14921643347</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>7171594</v>
+        <v>1145335</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>7580.02</v>
+        <v>6166.55</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>4323.47</v>
+        <v>1233.31</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>45872</v>
+        <v>45916</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>45872</v>
+        <v>45916</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>4323.47</v>
+        <v>1233.31</v>
       </c>
       <c r="AE8" s="3" t="inlineStr">
         <is>
@@ -4067,40 +4122,40 @@
         <v>0</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AH8" s="3" t="inlineStr"/>
       <c r="AI8" s="3" t="inlineStr"/>
       <c r="AJ8" s="3" t="n">
-        <v>560553</v>
+        <v>305096</v>
       </c>
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" s="4" t="n">
-        <v>45872</v>
+        <v>45916</v>
       </c>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="4" t="n">
-        <v>45872</v>
+        <v>45916</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>Ortopedia e Traumatologia</t>
+          <t>Dermatologia</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL - Plano Exemplo</t>
+          <t>RESIDENCIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>7171594</t>
+          <t>1145335</t>
         </is>
       </c>
       <c r="AT8" s="3" t="b">
@@ -4110,7 +4165,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>PROD-001437</t>
+          <t>PROD-001138</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -4119,11 +4174,11 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1437</v>
+        <v>1138</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>51713395962</t>
+          <t>14921643347</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -4138,7 +4193,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -4147,16 +4202,16 @@
         </is>
       </c>
       <c r="I9" s="6" t="n">
-        <v>45916</v>
+        <v>45873</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>538732</v>
+        <v>749987</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>45916</v>
+        <v>45873</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>46281</v>
+        <v>46238</v>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
@@ -4187,40 +4242,40 @@
       <c r="S9" s="5" t="inlineStr"/>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>Fernanda Almeida</t>
+          <t>Bruno Lima</t>
         </is>
       </c>
       <c r="U9" s="5" t="n">
-        <v>51713395962</v>
+        <v>14921643347</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>1145335</v>
+        <v>9203376</v>
       </c>
       <c r="W9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>6166.55</v>
+        <v>-209.5366856584408</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Z9" s="5" t="n">
-        <v>2586.47</v>
+        <v>760.29</v>
       </c>
       <c r="AA9" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="AB9" s="6" t="n">
-        <v>45916</v>
+        <v>45873</v>
       </c>
       <c r="AC9" s="6" t="n">
-        <v>45916</v>
+        <v>45873</v>
       </c>
       <c r="AD9" s="5" t="n">
-        <v>2586.47</v>
+        <v>760.29</v>
       </c>
       <c r="AE9" s="5" t="inlineStr">
         <is>
@@ -4231,30 +4286,30 @@
         <v>0</v>
       </c>
       <c r="AG9" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AH9" s="5" t="inlineStr"/>
       <c r="AI9" s="5" t="inlineStr"/>
       <c r="AJ9" s="5" t="n">
-        <v>305096</v>
+        <v>752862</v>
       </c>
       <c r="AK9" s="5" t="inlineStr"/>
       <c r="AL9" s="6" t="n">
-        <v>45916</v>
+        <v>45873</v>
       </c>
       <c r="AM9" s="5" t="inlineStr"/>
       <c r="AN9" s="6" t="n">
-        <v>45916</v>
+        <v>45873</v>
       </c>
       <c r="AO9" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP9" s="5" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="AQ9" s="5" t="inlineStr">
         <is>
-          <t>Otorrinolaringologia</t>
+          <t>Dermatologia</t>
         </is>
       </c>
       <c r="AR9" s="5" t="inlineStr">
@@ -4264,7 +4319,7 @@
       </c>
       <c r="AS9" s="5" t="inlineStr">
         <is>
-          <t>1145335</t>
+          <t>9203376</t>
         </is>
       </c>
       <c r="AT9" s="5" t="b">
@@ -4274,7 +4329,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>PROD-001438</t>
+          <t>PROD-001258</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -4283,16 +4338,16 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1438</v>
+        <v>1258</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>51713395962</t>
+          <t>88615335554</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -4302,7 +4357,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>PATRIMONIAL</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -4311,20 +4366,20 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>749987</v>
+        <v>598984</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -4351,40 +4406,40 @@
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Fernanda Almeida</t>
+          <t>Yara Souza</t>
         </is>
       </c>
       <c r="U10" s="3" t="n">
-        <v>51713395962</v>
+        <v>88615335554</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>9203376</v>
+        <v>3983710</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>6335.77</v>
+        <v>5693.24</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>760.29</v>
+        <v>7742.39</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="AC10" s="4" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>760.29</v>
+        <v>7742.39</v>
       </c>
       <c r="AE10" s="3" t="inlineStr">
         <is>
@@ -4395,30 +4450,30 @@
         <v>0</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH10" s="3" t="inlineStr"/>
       <c r="AI10" s="3" t="inlineStr"/>
       <c r="AJ10" s="3" t="n">
-        <v>752862</v>
+        <v>795167</v>
       </c>
       <c r="AK10" s="3" t="inlineStr"/>
       <c r="AL10" s="4" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="AM10" s="3" t="inlineStr"/>
       <c r="AN10" s="4" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>Otorrinolaringologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
@@ -4428,7 +4483,7 @@
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>9203376</t>
+          <t>3983710</t>
         </is>
       </c>
       <c r="AT10" s="3" t="b">
@@ -4438,7 +4493,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>PROD-001558</t>
+          <t>PROD-001278</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -4447,48 +4502,48 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1558</v>
+        <v>1278</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>12499856984</t>
+          <t>37693898331</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="I11" s="6" t="n">
-        <v>45883</v>
+        <v>45876</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>598984</v>
+        <v>200680</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>45883</v>
+        <v>45876</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>46248</v>
+        <v>46241</v>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -4515,40 +4570,40 @@
       <c r="S11" s="5" t="inlineStr"/>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>Vitor Costa</t>
+          <t>Tatiana Souza</t>
         </is>
       </c>
       <c r="U11" s="5" t="n">
-        <v>12499856984</v>
+        <v>37693898331</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>3983710</v>
+        <v>2707282</v>
       </c>
       <c r="W11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>5693.24</v>
+        <v>458.71</v>
       </c>
       <c r="Y11" s="5" t="n">
         <v>15</v>
       </c>
       <c r="Z11" s="5" t="n">
-        <v>853.99</v>
+        <v>68.81</v>
       </c>
       <c r="AA11" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="AB11" s="6" t="n">
-        <v>45883</v>
+        <v>45876</v>
       </c>
       <c r="AC11" s="6" t="n">
-        <v>45883</v>
+        <v>45876</v>
       </c>
       <c r="AD11" s="5" t="n">
-        <v>853.99</v>
+        <v>68.81</v>
       </c>
       <c r="AE11" s="5" t="inlineStr">
         <is>
@@ -4564,35 +4619,35 @@
       <c r="AH11" s="5" t="inlineStr"/>
       <c r="AI11" s="5" t="inlineStr"/>
       <c r="AJ11" s="5" t="n">
-        <v>795167</v>
+        <v>764376</v>
       </c>
       <c r="AK11" s="5" t="inlineStr"/>
       <c r="AL11" s="6" t="n">
-        <v>45883</v>
+        <v>45876</v>
       </c>
       <c r="AM11" s="5" t="inlineStr"/>
       <c r="AN11" s="6" t="n">
-        <v>45883</v>
+        <v>45876</v>
       </c>
       <c r="AO11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP11" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AQ11" s="5" t="inlineStr">
         <is>
-          <t>Otorrinolaringologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="AR11" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL - Plano Exemplo</t>
+          <t>EQUIPAMENTOS - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS11" s="5" t="inlineStr">
         <is>
-          <t>3983710</t>
+          <t>2707282</t>
         </is>
       </c>
       <c r="AT11" s="5" t="b">
@@ -4602,7 +4657,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>PROD-001578</t>
+          <t>PROD-001549</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -4611,11 +4666,11 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1578</v>
+        <v>1549</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>28699041379</t>
+          <t>01372151070</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -4625,30 +4680,30 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>45876</v>
+        <v>45866</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>200680</v>
+        <v>262742</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>45876</v>
+        <v>45866</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>46241</v>
+        <v>46231</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -4668,7 +4723,7 @@
       <c r="P12" s="3" t="inlineStr"/>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -4679,40 +4734,40 @@
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Gabriel Ferreira</t>
+          <t>Paulo Souza</t>
         </is>
       </c>
       <c r="U12" s="3" t="n">
-        <v>28699041379</v>
+        <v>1372151070</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>2707282</v>
+        <v>9755508</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>458.71</v>
+        <v>3425.27</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>68.81</v>
+        <v>411.03</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>45876</v>
+        <v>45866</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>45876</v>
+        <v>45866</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>68.81</v>
+        <v>411.03</v>
       </c>
       <c r="AE12" s="3" t="inlineStr">
         <is>
@@ -4728,35 +4783,35 @@
       <c r="AH12" s="3" t="inlineStr"/>
       <c r="AI12" s="3" t="inlineStr"/>
       <c r="AJ12" s="3" t="n">
-        <v>764376</v>
+        <v>252328</v>
       </c>
       <c r="AK12" s="3" t="inlineStr"/>
       <c r="AL12" s="4" t="n">
-        <v>45876</v>
+        <v>45866</v>
       </c>
       <c r="AM12" s="3" t="inlineStr"/>
       <c r="AN12" s="4" t="n">
-        <v>45876</v>
+        <v>45866</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP12" s="3" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>Pediatria</t>
+          <t>Otorrinolaringologia</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>2707282</t>
+          <t>9755508</t>
         </is>
       </c>
       <c r="AT12" s="3" t="b">
@@ -4766,7 +4821,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>PROD-001849</t>
+          <t>PROD-001639</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -4775,48 +4830,48 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1849</v>
+        <v>1639</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>13858542493</t>
+          <t>18102203173</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="I13" s="6" t="n">
-        <v>45866</v>
+        <v>45851</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>262742</v>
+        <v>758641</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>45866</v>
+        <v>45851</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>46231</v>
+        <v>46216</v>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
@@ -4832,7 +4887,7 @@
       <c r="P13" s="5" t="inlineStr"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
@@ -4843,40 +4898,40 @@
       <c r="S13" s="5" t="inlineStr"/>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Carla Ferreira</t>
         </is>
       </c>
       <c r="U13" s="5" t="n">
-        <v>13858542493</v>
+        <v>18102203173</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>9755508</v>
+        <v>5402331</v>
       </c>
       <c r="W13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>3425.27</v>
+        <v>2594.16</v>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z13" s="5" t="n">
-        <v>411.03</v>
+        <v>259.42</v>
       </c>
       <c r="AA13" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="AB13" s="6" t="n">
-        <v>45866</v>
+        <v>45851</v>
       </c>
       <c r="AC13" s="6" t="n">
-        <v>45866</v>
+        <v>45851</v>
       </c>
       <c r="AD13" s="5" t="n">
-        <v>411.03</v>
+        <v>259.42</v>
       </c>
       <c r="AE13" s="5" t="inlineStr">
         <is>
@@ -4892,35 +4947,35 @@
       <c r="AH13" s="5" t="inlineStr"/>
       <c r="AI13" s="5" t="inlineStr"/>
       <c r="AJ13" s="5" t="n">
-        <v>252328</v>
+        <v>758607</v>
       </c>
       <c r="AK13" s="5" t="inlineStr"/>
       <c r="AL13" s="6" t="n">
-        <v>45866</v>
+        <v>45851</v>
       </c>
       <c r="AM13" s="5" t="inlineStr"/>
       <c r="AN13" s="6" t="n">
-        <v>45866</v>
+        <v>45851</v>
       </c>
       <c r="AO13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP13" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ13" s="5" t="inlineStr">
         <is>
-          <t>Ginecologia e Obstetrícia</t>
+          <t>Cirurgia Geral</t>
         </is>
       </c>
       <c r="AR13" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL - Plano Exemplo</t>
+          <t>RESIDENCIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS13" s="5" t="inlineStr">
         <is>
-          <t>9755508</t>
+          <t>5402331</t>
         </is>
       </c>
       <c r="AT13" s="5" t="b">
@@ -4930,7 +4985,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>PROD-001939</t>
+          <t>PROD-001776</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -4939,16 +4994,16 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1939</v>
+        <v>1776</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>25534192832</t>
+          <t>22820055778</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -4958,7 +5013,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -4967,20 +5022,20 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>45851</v>
+        <v>45854</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>758641</v>
+        <v>267895</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>45851</v>
+        <v>45854</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -5007,40 +5062,40 @@
       <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>Rafaela Rodrigues</t>
+          <t>Nelson Martins</t>
         </is>
       </c>
       <c r="U14" s="3" t="n">
-        <v>25534192832</v>
+        <v>22820055778</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>5402331</v>
+        <v>7047367</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>2594.16</v>
+        <v>8452.059999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>259.42</v>
+        <v>1267.81</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>45851</v>
+        <v>45854</v>
       </c>
       <c r="AC14" s="4" t="n">
-        <v>45851</v>
+        <v>45854</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>259.42</v>
+        <v>1267.81</v>
       </c>
       <c r="AE14" s="3" t="inlineStr">
         <is>
@@ -5051,30 +5106,30 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AH14" s="3" t="inlineStr"/>
       <c r="AI14" s="3" t="inlineStr"/>
       <c r="AJ14" s="3" t="n">
-        <v>758607</v>
+        <v>216556</v>
       </c>
       <c r="AK14" s="3" t="inlineStr"/>
       <c r="AL14" s="4" t="n">
-        <v>45851</v>
+        <v>45854</v>
       </c>
       <c r="AM14" s="3" t="inlineStr"/>
       <c r="AN14" s="4" t="n">
-        <v>45851</v>
+        <v>45854</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP14" s="3" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>Neurologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
@@ -5084,7 +5139,7 @@
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>5402331</t>
+          <t>7047367</t>
         </is>
       </c>
       <c r="AT14" s="3" t="b">
@@ -5094,7 +5149,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROD-002076</t>
+          <t>PROD-001835</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -5103,48 +5158,48 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2076</v>
+        <v>1835</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>15890429025</t>
+          <t>22535841438</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>45854</v>
+        <v>45834</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>267895</v>
+        <v>280510</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>45854</v>
+        <v>45834</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>46219</v>
+        <v>46199</v>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
@@ -5171,40 +5226,40 @@
       <c r="S15" s="5" t="inlineStr"/>
       <c r="T15" s="5" t="inlineStr">
         <is>
-          <t>Fernanda Costa</t>
+          <t>Ana Ferreira</t>
         </is>
       </c>
       <c r="U15" s="5" t="n">
-        <v>15890429025</v>
+        <v>22535841438</v>
       </c>
       <c r="V15" s="5" t="n">
-        <v>7047367</v>
+        <v>37426102025</v>
       </c>
       <c r="W15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X15" s="5" t="n">
-        <v>8452.059999999999</v>
+        <v>5218.51</v>
       </c>
       <c r="Y15" s="5" t="n">
         <v>15</v>
       </c>
       <c r="Z15" s="5" t="n">
-        <v>1267.81</v>
+        <v>782.78</v>
       </c>
       <c r="AA15" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="AB15" s="6" t="n">
-        <v>45854</v>
+        <v>45834</v>
       </c>
       <c r="AC15" s="6" t="n">
-        <v>45854</v>
+        <v>45834</v>
       </c>
       <c r="AD15" s="5" t="n">
-        <v>1267.81</v>
+        <v>782.78</v>
       </c>
       <c r="AE15" s="5" t="inlineStr">
         <is>
@@ -5215,40 +5270,40 @@
         <v>0</v>
       </c>
       <c r="AG15" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH15" s="5" t="inlineStr"/>
       <c r="AI15" s="5" t="inlineStr"/>
       <c r="AJ15" s="5" t="n">
-        <v>216556</v>
+        <v>112535</v>
       </c>
       <c r="AK15" s="5" t="inlineStr"/>
       <c r="AL15" s="6" t="n">
-        <v>45854</v>
+        <v>45834</v>
       </c>
       <c r="AM15" s="5" t="inlineStr"/>
       <c r="AN15" s="6" t="n">
-        <v>45854</v>
+        <v>45834</v>
       </c>
       <c r="AO15" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP15" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AQ15" s="5" t="inlineStr">
         <is>
-          <t>Ginecologia e Obstetrícia</t>
+          <t>Anestesiologia</t>
         </is>
       </c>
       <c r="AR15" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS15" s="5" t="inlineStr">
         <is>
-          <t>7047367</t>
+          <t>3742610</t>
         </is>
       </c>
       <c r="AT15" s="5" t="b">
@@ -5258,7 +5313,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>PROD-002135</t>
+          <t>PROD-001871</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -5267,48 +5322,48 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2135</v>
+        <v>1871</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>68011280598</t>
+          <t>09859317461</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>45834</v>
+        <v>45891</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>280510</v>
+        <v>979677</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>45834</v>
+        <v>45891</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>46199</v>
+        <v>46256</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>ZETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -5335,40 +5390,40 @@
       <c r="S16" s="3" t="inlineStr"/>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>Tatiana Oliveira</t>
+          <t>Lucas Rodrigues</t>
         </is>
       </c>
       <c r="U16" s="3" t="n">
-        <v>68011280598</v>
+        <v>9859317461</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>37426102025</v>
+        <v>3416872</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>5218.51</v>
+        <v>3293.99</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>782.78</v>
+        <v>494.1</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>45834</v>
+        <v>45891</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>45834</v>
+        <v>45891</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>782.78</v>
+        <v>494.1</v>
       </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
@@ -5379,40 +5434,40 @@
         <v>0</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AH16" s="3" t="inlineStr"/>
       <c r="AI16" s="3" t="inlineStr"/>
       <c r="AJ16" s="3" t="n">
-        <v>112535</v>
+        <v>567679</v>
       </c>
       <c r="AK16" s="3" t="inlineStr"/>
       <c r="AL16" s="4" t="n">
-        <v>45834</v>
+        <v>45891</v>
       </c>
       <c r="AM16" s="3" t="inlineStr"/>
       <c r="AN16" s="4" t="n">
-        <v>45834</v>
+        <v>45891</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP16" s="3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>Endocrinologia</t>
+          <t>Cirurgia Geral</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL - Plano Exemplo</t>
+          <t>RC PROFISSIONAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>3742610</t>
+          <t>3416872</t>
         </is>
       </c>
       <c r="AT16" s="3" t="b">
@@ -5422,7 +5477,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>PROD-002171</t>
+          <t>PROD-001905</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -5431,48 +5486,48 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2171</v>
+        <v>1905</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>52056647423</t>
+          <t>42843479552</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="I17" s="6" t="n">
-        <v>45891</v>
+        <v>45877</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>979677</v>
+        <v>885354</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>45891</v>
+        <v>45877</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>46256</v>
+        <v>46242</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
@@ -5488,7 +5543,7 @@
       <c r="P17" s="5" t="inlineStr"/>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R17" s="5" t="inlineStr">
@@ -5499,40 +5554,40 @@
       <c r="S17" s="5" t="inlineStr"/>
       <c r="T17" s="5" t="inlineStr">
         <is>
-          <t>Ana Souza</t>
+          <t>Vitor Rodrigues</t>
         </is>
       </c>
       <c r="U17" s="5" t="n">
-        <v>52056647423</v>
+        <v>42843479552</v>
       </c>
       <c r="V17" s="5" t="n">
-        <v>3416872</v>
+        <v>7402777</v>
       </c>
       <c r="W17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X17" s="5" t="n">
-        <v>3293.99</v>
+        <v>7846.91</v>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z17" s="5" t="n">
-        <v>4973.87</v>
+        <v>941.63</v>
       </c>
       <c r="AA17" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="AB17" s="6" t="n">
-        <v>45891</v>
+        <v>45877</v>
       </c>
       <c r="AC17" s="6" t="n">
-        <v>45891</v>
+        <v>45877</v>
       </c>
       <c r="AD17" s="5" t="n">
-        <v>4973.87</v>
+        <v>941.63</v>
       </c>
       <c r="AE17" s="5" t="inlineStr">
         <is>
@@ -5548,35 +5603,35 @@
       <c r="AH17" s="5" t="inlineStr"/>
       <c r="AI17" s="5" t="inlineStr"/>
       <c r="AJ17" s="5" t="n">
-        <v>567679</v>
+        <v>925908</v>
       </c>
       <c r="AK17" s="5" t="inlineStr"/>
       <c r="AL17" s="6" t="n">
-        <v>45891</v>
+        <v>45877</v>
       </c>
       <c r="AM17" s="5" t="inlineStr"/>
       <c r="AN17" s="6" t="n">
-        <v>45891</v>
+        <v>45877</v>
       </c>
       <c r="AO17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP17" s="5" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AQ17" s="5" t="inlineStr">
         <is>
-          <t>Radiologia</t>
+          <t>Neurologia</t>
         </is>
       </c>
       <c r="AR17" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL - Plano Exemplo</t>
+          <t>RESIDENCIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS17" s="5" t="inlineStr">
         <is>
-          <t>3416872</t>
+          <t>7402777</t>
         </is>
       </c>
       <c r="AT17" s="5" t="b">
@@ -5586,7 +5641,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>PROD-002205</t>
+          <t>PROD-002132</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -5595,16 +5650,16 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2205</v>
+        <v>2132</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>47284639208</t>
+          <t>89994043898</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -5614,7 +5669,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -5623,20 +5678,20 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>45877</v>
+        <v>45918</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>885354</v>
+        <v>964314</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>45877</v>
+        <v>45918</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>46242</v>
+        <v>46283</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -5652,7 +5707,7 @@
       <c r="P18" s="3" t="inlineStr"/>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -5663,74 +5718,74 @@
       <c r="S18" s="3" t="inlineStr"/>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>Igor Silva</t>
+          <t>Daniel Rodrigues</t>
         </is>
       </c>
       <c r="U18" s="3" t="n">
-        <v>47284639208</v>
+        <v>89994043898</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>7402777</v>
+        <v>3767919</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>7846.91</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>74.83</v>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Diego Comercial</t>
+        </is>
+      </c>
+      <c r="AB18" s="4" t="n">
+        <v>45918</v>
+      </c>
+      <c r="AC18" s="4" t="n">
+        <v>45918</v>
+      </c>
+      <c r="AD18" s="3" t="n">
+        <v>74.83</v>
+      </c>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>usuario.exemplo</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3" t="n">
         <v>12</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>1683.32</v>
-      </c>
-      <c r="AA18" s="3" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="AB18" s="4" t="n">
-        <v>45877</v>
-      </c>
-      <c r="AC18" s="4" t="n">
-        <v>45877</v>
-      </c>
-      <c r="AD18" s="3" t="n">
-        <v>1683.32</v>
-      </c>
-      <c r="AE18" s="3" t="inlineStr">
-        <is>
-          <t>usuario.exemplo</t>
-        </is>
-      </c>
-      <c r="AF18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="3" t="n">
-        <v>6</v>
       </c>
       <c r="AH18" s="3" t="inlineStr"/>
       <c r="AI18" s="3" t="inlineStr"/>
       <c r="AJ18" s="3" t="n">
-        <v>925908</v>
+        <v>894360</v>
       </c>
       <c r="AK18" s="3" t="inlineStr"/>
       <c r="AL18" s="4" t="n">
-        <v>45877</v>
+        <v>45918</v>
       </c>
       <c r="AM18" s="3" t="inlineStr"/>
       <c r="AN18" s="4" t="n">
-        <v>45877</v>
+        <v>45918</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP18" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>Radiologia</t>
+          <t>Anestesiologia</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
@@ -5740,7 +5795,7 @@
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>7402777</t>
+          <t>3767919</t>
         </is>
       </c>
       <c r="AT18" s="3" t="b">
@@ -5750,7 +5805,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>PROD-002432</t>
+          <t>PROD-002486</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -5759,48 +5814,48 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2432</v>
+        <v>2486</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>54868740345</t>
+          <t>31752071678</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>964314</v>
+        <v>801613</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>46283</v>
+        <v>46227</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -5827,40 +5882,40 @@
       <c r="S19" s="5" t="inlineStr"/>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t>Sérgio Gomes</t>
+          <t>Daniel Almeida</t>
         </is>
       </c>
       <c r="U19" s="5" t="n">
-        <v>54868740345</v>
+        <v>31752071678</v>
       </c>
       <c r="V19" s="5" t="n">
-        <v>3767919</v>
+        <v>49823142025</v>
       </c>
       <c r="W19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X19" s="5" t="n">
-        <v>498.86</v>
+        <v>6461.01</v>
       </c>
       <c r="Y19" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z19" s="5" t="n">
-        <v>74.83</v>
+        <v>1292.2</v>
       </c>
       <c r="AA19" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="AB19" s="6" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="AC19" s="6" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="AD19" s="5" t="n">
-        <v>74.83</v>
+        <v>1292.2</v>
       </c>
       <c r="AE19" s="5" t="inlineStr">
         <is>
@@ -5871,40 +5926,40 @@
         <v>0</v>
       </c>
       <c r="AG19" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH19" s="5" t="inlineStr"/>
       <c r="AI19" s="5" t="inlineStr"/>
       <c r="AJ19" s="5" t="n">
-        <v>894360</v>
+        <v>102557</v>
       </c>
       <c r="AK19" s="5" t="inlineStr"/>
       <c r="AL19" s="6" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="AM19" s="5" t="inlineStr"/>
       <c r="AN19" s="6" t="n">
-        <v>45918</v>
+        <v>45862</v>
       </c>
       <c r="AO19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP19" s="5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ19" s="5" t="inlineStr">
         <is>
-          <t>Urologia</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="AR19" s="5" t="inlineStr">
         <is>
-          <t>RESIDENCIAL - Plano Exemplo</t>
+          <t>EQUIPAMENTOS - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS19" s="5" t="inlineStr">
         <is>
-          <t>3767919</t>
+          <t>4982314</t>
         </is>
       </c>
       <c r="AT19" s="5" t="b">
@@ -5914,7 +5969,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>PROD-002786</t>
+          <t>PROD-002487</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -5923,38 +5978,38 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2786</v>
+        <v>2487</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>63942788165</t>
+          <t>60466183982</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>RC PROFISSIONAL</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
         <v>45862</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>801613</v>
+        <v>360535</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>45862</v>
@@ -5964,7 +6019,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -5991,30 +6046,30 @@
       <c r="S20" s="3" t="inlineStr"/>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>Helena Silva</t>
+          <t>Júlia Almeida</t>
         </is>
       </c>
       <c r="U20" s="3" t="n">
-        <v>63942788165</v>
+        <v>60466183982</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>49823142025</v>
+        <v>8546302</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>6461.01</v>
+        <v>2764.94</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>1292.2</v>
+        <v>414.74</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="AB20" s="4" t="n">
@@ -6024,7 +6079,7 @@
         <v>45862</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>1292.2</v>
+        <v>414.74</v>
       </c>
       <c r="AE20" s="3" t="inlineStr">
         <is>
@@ -6035,12 +6090,12 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH20" s="3" t="inlineStr"/>
       <c r="AI20" s="3" t="inlineStr"/>
       <c r="AJ20" s="3" t="n">
-        <v>102557</v>
+        <v>553275</v>
       </c>
       <c r="AK20" s="3" t="inlineStr"/>
       <c r="AL20" s="4" t="n">
@@ -6054,21 +6109,21 @@
         <v>1</v>
       </c>
       <c r="AP20" s="3" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>Psiquiatria</t>
+          <t>Radiologia</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS - Plano Exemplo</t>
+          <t>RC PROFISSIONAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>4982314</t>
+          <t>8546302</t>
         </is>
       </c>
       <c r="AT20" s="3" t="b">
@@ -6078,7 +6133,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>PROD-002787</t>
+          <t>PROD-002986</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -6087,48 +6142,48 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2787</v>
+        <v>2986</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>85642059304</t>
+          <t>87719065940</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="I21" s="6" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>360535</v>
+        <v>468934</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>46227</v>
+        <v>46206</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
@@ -6144,7 +6199,7 @@
       <c r="P21" s="5" t="inlineStr"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R21" s="5" t="inlineStr">
@@ -6155,40 +6210,40 @@
       <c r="S21" s="5" t="inlineStr"/>
       <c r="T21" s="5" t="inlineStr">
         <is>
-          <t>Olívia Rodrigues</t>
+          <t>Ana Pereira</t>
         </is>
       </c>
       <c r="U21" s="5" t="n">
-        <v>85642059304</v>
+        <v>87719065940</v>
       </c>
       <c r="V21" s="5" t="n">
-        <v>8546302</v>
+        <v>7129228</v>
       </c>
       <c r="W21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X21" s="5" t="n">
-        <v>2764.94</v>
+        <v>7049.86</v>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z21" s="5" t="n">
-        <v>414.74</v>
+        <v>704.99</v>
       </c>
       <c r="AA21" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="AB21" s="6" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="AC21" s="6" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="AD21" s="5" t="n">
-        <v>414.74</v>
+        <v>704.99</v>
       </c>
       <c r="AE21" s="5" t="inlineStr">
         <is>
@@ -6204,35 +6259,35 @@
       <c r="AH21" s="5" t="inlineStr"/>
       <c r="AI21" s="5" t="inlineStr"/>
       <c r="AJ21" s="5" t="n">
-        <v>553275</v>
+        <v>764704</v>
       </c>
       <c r="AK21" s="5" t="inlineStr"/>
       <c r="AL21" s="6" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="AM21" s="5" t="inlineStr"/>
       <c r="AN21" s="6" t="n">
-        <v>45862</v>
+        <v>45841</v>
       </c>
       <c r="AO21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP21" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AQ21" s="5" t="inlineStr">
         <is>
-          <t>Oftalmologia</t>
+          <t>Anestesiologia</t>
         </is>
       </c>
       <c r="AR21" s="5" t="inlineStr">
         <is>
-          <t>RC PROFISSIONAL - Plano Exemplo</t>
+          <t>EMPRESARIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS21" s="5" t="inlineStr">
         <is>
-          <t>8546302</t>
+          <t>7129228</t>
         </is>
       </c>
       <c r="AT21" s="5" t="b">
@@ -6242,7 +6297,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>PROD-003286</t>
+          <t>PROD-003261</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -6251,11 +6306,11 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>3286</v>
+        <v>3261</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>76617711592</t>
+          <t>13736785082</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -6265,7 +6320,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -6275,20 +6330,20 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>45841</v>
+        <v>45913</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>468934</v>
+        <v>923620</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>45841</v>
+        <v>45913</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>46206</v>
+        <v>46278</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -6308,7 +6363,7 @@
       <c r="P22" s="3" t="inlineStr"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
@@ -6319,40 +6374,40 @@
       <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>Paulo Pereira</t>
+          <t>Mariana Almeida</t>
         </is>
       </c>
       <c r="U22" s="3" t="n">
-        <v>76617711592</v>
+        <v>13736785082</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>7129228</v>
+        <v>2171603</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>7049.86</v>
+        <v>6204.82</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>704.99</v>
+        <v>930.72</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>45841</v>
+        <v>45913</v>
       </c>
       <c r="AC22" s="4" t="n">
-        <v>45841</v>
+        <v>45913</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>704.99</v>
+        <v>930.72</v>
       </c>
       <c r="AE22" s="3" t="inlineStr">
         <is>
@@ -6363,40 +6418,40 @@
         <v>0</v>
       </c>
       <c r="AG22" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH22" s="3" t="inlineStr"/>
       <c r="AI22" s="3" t="inlineStr"/>
       <c r="AJ22" s="3" t="n">
-        <v>764704</v>
+        <v>452700</v>
       </c>
       <c r="AK22" s="3" t="inlineStr"/>
       <c r="AL22" s="4" t="n">
-        <v>45841</v>
+        <v>45913</v>
       </c>
       <c r="AM22" s="3" t="inlineStr"/>
       <c r="AN22" s="4" t="n">
-        <v>45841</v>
+        <v>45913</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP22" s="3" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>Radiologia</t>
+          <t>Cardiologia</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>EMPRESARIAL - Plano Exemplo</t>
+          <t>RESIDENCIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>7129228</t>
+          <t>2171603</t>
         </is>
       </c>
       <c r="AT22" s="3" t="b">
@@ -6406,7 +6461,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>PROD-003542</t>
+          <t>PROD-003485</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -6415,48 +6470,48 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>3542</v>
+        <v>3485</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>37562890028</t>
+          <t>26368970283</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>PATRIMONIAL</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="I23" s="6" t="n">
-        <v>45750</v>
+        <v>45866</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>622379</v>
+        <v>469093</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>45750</v>
+        <v>45866</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>46115</v>
+        <v>46231</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
@@ -6483,40 +6538,40 @@
       <c r="S23" s="5" t="inlineStr"/>
       <c r="T23" s="5" t="inlineStr">
         <is>
-          <t>Ana Oliveira</t>
+          <t>Yara Martins</t>
         </is>
       </c>
       <c r="U23" s="5" t="n">
-        <v>37562890028</v>
+        <v>26368970283</v>
       </c>
       <c r="V23" s="5" t="n">
-        <v>5420147</v>
+        <v>6558135</v>
       </c>
       <c r="W23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X23" s="5" t="n">
-        <v>2440.79</v>
+        <v>323.15</v>
       </c>
       <c r="Y23" s="5" t="n">
         <v>30</v>
       </c>
       <c r="Z23" s="5" t="n">
-        <v>732.24</v>
+        <v>389.68</v>
       </c>
       <c r="AA23" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="AB23" s="6" t="n">
-        <v>45750</v>
+        <v>45866</v>
       </c>
       <c r="AC23" s="6" t="n">
-        <v>45750</v>
+        <v>45866</v>
       </c>
       <c r="AD23" s="5" t="n">
-        <v>732.24</v>
+        <v>389.68</v>
       </c>
       <c r="AE23" s="5" t="inlineStr">
         <is>
@@ -6527,40 +6582,40 @@
         <v>0</v>
       </c>
       <c r="AG23" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH23" s="5" t="inlineStr"/>
       <c r="AI23" s="5" t="inlineStr"/>
       <c r="AJ23" s="5" t="n">
-        <v>652819</v>
+        <v>270751</v>
       </c>
       <c r="AK23" s="5" t="inlineStr"/>
       <c r="AL23" s="6" t="n">
-        <v>45750</v>
+        <v>45866</v>
       </c>
       <c r="AM23" s="5" t="inlineStr"/>
       <c r="AN23" s="6" t="n">
-        <v>45750</v>
+        <v>45866</v>
       </c>
       <c r="AO23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP23" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ23" s="5" t="inlineStr">
         <is>
-          <t>Psiquiatria</t>
+          <t>Oftalmologia</t>
         </is>
       </c>
       <c r="AR23" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL - Plano Exemplo</t>
+          <t>EQUIPAMENTOS - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS23" s="5" t="inlineStr">
         <is>
-          <t>5420147</t>
+          <t>6558135</t>
         </is>
       </c>
       <c r="AT23" s="5" t="b">
@@ -6570,7 +6625,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>PROD-003561</t>
+          <t>PROD-003786</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6579,16 +6634,16 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>3561</v>
+        <v>3786</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>75901751863</t>
+          <t>65094801413</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -6598,7 +6653,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -6607,20 +6662,20 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>45913</v>
+        <v>45892</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>923620</v>
+        <v>474147</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>45913</v>
+        <v>45892</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>46278</v>
+        <v>46257</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -6636,7 +6691,7 @@
       <c r="P24" s="3" t="inlineStr"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
@@ -6647,40 +6702,40 @@
       <c r="S24" s="3" t="inlineStr"/>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>Júlia Lima</t>
+          <t>Igor Souza</t>
         </is>
       </c>
       <c r="U24" s="3" t="n">
-        <v>75901751863</v>
+        <v>65094801413</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>2171603</v>
+        <v>3480382</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>6204.82</v>
+        <v>1616.84</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>930.72</v>
+        <v>404.21</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Ana Vendas</t>
         </is>
       </c>
       <c r="AB24" s="4" t="n">
-        <v>45913</v>
+        <v>45892</v>
       </c>
       <c r="AC24" s="4" t="n">
-        <v>45913</v>
+        <v>45892</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>930.72</v>
+        <v>404.21</v>
       </c>
       <c r="AE24" s="3" t="inlineStr">
         <is>
@@ -6696,25 +6751,25 @@
       <c r="AH24" s="3" t="inlineStr"/>
       <c r="AI24" s="3" t="inlineStr"/>
       <c r="AJ24" s="3" t="n">
-        <v>452700</v>
+        <v>936111</v>
       </c>
       <c r="AK24" s="3" t="inlineStr"/>
       <c r="AL24" s="4" t="n">
-        <v>45913</v>
+        <v>45892</v>
       </c>
       <c r="AM24" s="3" t="inlineStr"/>
       <c r="AN24" s="4" t="n">
-        <v>45913</v>
+        <v>45892</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP24" s="3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>Radiologia</t>
+          <t>Cardiologia</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
@@ -6724,7 +6779,7 @@
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>2171603</t>
+          <t>3480382</t>
         </is>
       </c>
       <c r="AT24" s="3" t="b">
@@ -6734,7 +6789,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>PROD-003785</t>
+          <t>PROD-003840</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -6743,11 +6798,11 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>3785</v>
+        <v>3840</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>56704310385</t>
+          <t>67883171210</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -6757,30 +6812,30 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>PREVIDÊNCIA</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="I25" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>469093</v>
+        <v>628741</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>46231</v>
+        <v>46217</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
@@ -6800,7 +6855,7 @@
       <c r="P25" s="5" t="inlineStr"/>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R25" s="5" t="inlineStr">
@@ -6811,40 +6866,40 @@
       <c r="S25" s="5" t="inlineStr"/>
       <c r="T25" s="5" t="inlineStr">
         <is>
-          <t>Bruno Gomes</t>
+          <t>Rafaela Souza</t>
         </is>
       </c>
       <c r="U25" s="5" t="n">
-        <v>56704310385</v>
+        <v>67883171210</v>
       </c>
       <c r="V25" s="5" t="n">
-        <v>6558135</v>
+        <v>9813864</v>
       </c>
       <c r="W25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X25" s="5" t="n">
-        <v>323.15</v>
+        <v>8271.17</v>
       </c>
       <c r="Y25" s="5" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="Z25" s="5" t="n">
-        <v>96.94</v>
+        <v>1488.81</v>
       </c>
       <c r="AA25" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="AB25" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="AC25" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="AD25" s="5" t="n">
-        <v>96.94</v>
+        <v>1488.81</v>
       </c>
       <c r="AE25" s="5" t="inlineStr">
         <is>
@@ -6855,40 +6910,40 @@
         <v>0</v>
       </c>
       <c r="AG25" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH25" s="5" t="inlineStr"/>
       <c r="AI25" s="5" t="inlineStr"/>
       <c r="AJ25" s="5" t="n">
-        <v>270751</v>
+        <v>763637</v>
       </c>
       <c r="AK25" s="5" t="inlineStr"/>
       <c r="AL25" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="AM25" s="5" t="inlineStr"/>
       <c r="AN25" s="6" t="n">
-        <v>45866</v>
+        <v>45852</v>
       </c>
       <c r="AO25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP25" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AQ25" s="5" t="inlineStr">
         <is>
-          <t>Endocrinologia</t>
+          <t>Ortopedia e Traumatologia</t>
         </is>
       </c>
       <c r="AR25" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS - Plano Exemplo</t>
+          <t>EMPRESARIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS25" s="5" t="inlineStr">
         <is>
-          <t>6558135</t>
+          <t>9813864</t>
         </is>
       </c>
       <c r="AT25" s="5" t="b">
@@ -6898,7 +6953,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>PROD-004086</t>
+          <t>PROD-004020</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6907,21 +6962,21 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>4086</v>
+        <v>4020</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>08589944171</t>
+          <t>77418625652</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -6931,24 +6986,24 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>474147</v>
+        <v>442395</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>46257</v>
+        <v>46267</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>GAMA</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -6975,40 +7030,40 @@
       <c r="S26" s="3" t="inlineStr"/>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>Carla Souza</t>
+          <t>Eduardo Ferreira</t>
         </is>
       </c>
       <c r="U26" s="3" t="n">
-        <v>8589944171</v>
+        <v>77418625652</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>3480382</v>
+        <v>7314480</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>1616.84</v>
+        <v>7115.43</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>404.21</v>
+        <v>1423.09</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="AB26" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="AC26" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>404.21</v>
+        <v>1423.09</v>
       </c>
       <c r="AE26" s="3" t="inlineStr">
         <is>
@@ -7019,40 +7074,40 @@
         <v>0</v>
       </c>
       <c r="AG26" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH26" s="3" t="inlineStr"/>
       <c r="AI26" s="3" t="inlineStr"/>
       <c r="AJ26" s="3" t="n">
-        <v>936111</v>
+        <v>516129</v>
       </c>
       <c r="AK26" s="3" t="inlineStr"/>
       <c r="AL26" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="AM26" s="3" t="inlineStr"/>
       <c r="AN26" s="4" t="n">
-        <v>45892</v>
+        <v>45902</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP26" s="3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>Oftalmologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>3480382</t>
+          <t>7314480</t>
         </is>
       </c>
       <c r="AT26" s="3" t="b">
@@ -7062,7 +7117,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>PROD-004140</t>
+          <t>PROD-004079</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -7071,11 +7126,11 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>4140</v>
+        <v>4079</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>08240433504</t>
+          <t>57437489691</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -7085,7 +7140,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -7095,20 +7150,20 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I27" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>628741</v>
+        <v>877005</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>46217</v>
+        <v>46286</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
@@ -7128,7 +7183,7 @@
       <c r="P27" s="5" t="inlineStr"/>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R27" s="5" t="inlineStr">
@@ -7139,40 +7194,40 @@
       <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="5" t="inlineStr">
         <is>
-          <t>Yara Souza</t>
+          <t>Tatiana Martins</t>
         </is>
       </c>
       <c r="U27" s="5" t="n">
-        <v>8240433504</v>
+        <v>57437489691</v>
       </c>
       <c r="V27" s="5" t="n">
-        <v>9813864</v>
+        <v>3572267</v>
       </c>
       <c r="W27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X27" s="5" t="n">
-        <v>8271.17</v>
+        <v>4188.14</v>
       </c>
       <c r="Y27" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z27" s="5" t="n">
-        <v>1488.81</v>
+        <v>628.22</v>
       </c>
       <c r="AA27" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="AB27" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="AC27" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="AD27" s="5" t="n">
-        <v>1488.81</v>
+        <v>628.22</v>
       </c>
       <c r="AE27" s="5" t="inlineStr">
         <is>
@@ -7188,35 +7243,35 @@
       <c r="AH27" s="5" t="inlineStr"/>
       <c r="AI27" s="5" t="inlineStr"/>
       <c r="AJ27" s="5" t="n">
-        <v>763637</v>
+        <v>515999</v>
       </c>
       <c r="AK27" s="5" t="inlineStr"/>
       <c r="AL27" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="AM27" s="5" t="inlineStr"/>
       <c r="AN27" s="6" t="n">
-        <v>45852</v>
+        <v>45921</v>
       </c>
       <c r="AO27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP27" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AQ27" s="5" t="inlineStr">
         <is>
-          <t>Endocrinologia</t>
+          <t>Pediatria</t>
         </is>
       </c>
       <c r="AR27" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS27" s="5" t="inlineStr">
         <is>
-          <t>9813864</t>
+          <t>3572267</t>
         </is>
       </c>
       <c r="AT27" s="5" t="b">
@@ -7226,7 +7281,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>PROD-004320</t>
+          <t>PROD-004086</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -7235,48 +7290,48 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4320</v>
+        <v>4086</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>38657191826</t>
+          <t>32677360260</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>VIDA</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>RESIDENCIAL</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>442395</v>
+        <v>842857</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>46267</v>
+        <v>46235</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>GAMA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -7303,40 +7358,40 @@
       <c r="S28" s="3" t="inlineStr"/>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>Ana Almeida</t>
+          <t>Rafaela Martins</t>
         </is>
       </c>
       <c r="U28" s="3" t="n">
-        <v>38657191826</v>
+        <v>32677360260</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>7314480</v>
+        <v>9154494</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>7115.43</v>
+        <v>3165.12</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>1423.09</v>
+        <v>379.81</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="AC28" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>1423.09</v>
+        <v>379.81</v>
       </c>
       <c r="AE28" s="3" t="inlineStr">
         <is>
@@ -7347,26 +7402,26 @@
         <v>0</v>
       </c>
       <c r="AG28" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH28" s="3" t="inlineStr"/>
       <c r="AI28" s="3" t="inlineStr"/>
       <c r="AJ28" s="3" t="n">
-        <v>516129</v>
+        <v>964618</v>
       </c>
       <c r="AK28" s="3" t="inlineStr"/>
       <c r="AL28" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="AM28" s="3" t="inlineStr"/>
       <c r="AN28" s="4" t="n">
-        <v>45902</v>
+        <v>45870</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP28" s="3" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
@@ -7375,12 +7430,12 @@
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL - Plano Exemplo</t>
+          <t>RESIDENCIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>7314480</t>
+          <t>9154494</t>
         </is>
       </c>
       <c r="AT28" s="3" t="b">
@@ -7390,7 +7445,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>PROD-004379</t>
+          <t>PROD-004106</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -7399,48 +7454,48 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>4379</v>
+        <v>4106</v>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>85368663266</t>
+          <t>04341651827</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>PREVIDÊNCIA</t>
+          <t>VIAGEM</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL</t>
+          <t>EMPRESARIAL</t>
         </is>
       </c>
       <c r="I29" s="6" t="n">
-        <v>45921</v>
+        <v>45886</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>877005</v>
+        <v>901247</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>45921</v>
+        <v>45886</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>46286</v>
+        <v>46251</v>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -7456,7 +7511,7 @@
       <c r="P29" s="5" t="inlineStr"/>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr">
@@ -7467,40 +7522,40 @@
       <c r="S29" s="5" t="inlineStr"/>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t>Rafaela Lima</t>
+          <t>Tatiana Ferreira</t>
         </is>
       </c>
       <c r="U29" s="5" t="n">
-        <v>85368663266</v>
+        <v>4341651827</v>
       </c>
       <c r="V29" s="5" t="n">
-        <v>3572267</v>
+        <v>91217802025</v>
       </c>
       <c r="W29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X29" s="5" t="n">
-        <v>4188.14</v>
+        <v>8185.23</v>
       </c>
       <c r="Y29" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z29" s="5" t="n">
-        <v>1407.64</v>
+        <v>1456.43</v>
       </c>
       <c r="AA29" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Carla Seguros</t>
         </is>
       </c>
       <c r="AB29" s="6" t="n">
-        <v>45921</v>
+        <v>45886</v>
       </c>
       <c r="AC29" s="6" t="n">
-        <v>45921</v>
+        <v>45886</v>
       </c>
       <c r="AD29" s="5" t="n">
-        <v>1407.64</v>
+        <v>1456.43</v>
       </c>
       <c r="AE29" s="5" t="inlineStr">
         <is>
@@ -7516,35 +7571,35 @@
       <c r="AH29" s="5" t="inlineStr"/>
       <c r="AI29" s="5" t="inlineStr"/>
       <c r="AJ29" s="5" t="n">
-        <v>515999</v>
+        <v>905448</v>
       </c>
       <c r="AK29" s="5" t="inlineStr"/>
       <c r="AL29" s="6" t="n">
-        <v>45921</v>
+        <v>45886</v>
       </c>
       <c r="AM29" s="5" t="inlineStr"/>
       <c r="AN29" s="6" t="n">
-        <v>45921</v>
+        <v>45886</v>
       </c>
       <c r="AO29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP29" s="5" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AQ29" s="5" t="inlineStr">
         <is>
-          <t>Psiquiatria</t>
+          <t>Radiologia</t>
         </is>
       </c>
       <c r="AR29" s="5" t="inlineStr">
         <is>
-          <t>AUTOMÓVEL - Plano Exemplo</t>
+          <t>EMPRESARIAL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS29" s="5" t="inlineStr">
         <is>
-          <t>3572267</t>
+          <t>9121780</t>
         </is>
       </c>
       <c r="AT29" s="5" t="b">
@@ -7554,7 +7609,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>PROD-004386</t>
+          <t>PROD-004108</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -7563,16 +7618,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4386</v>
+        <v>4108</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>89026012796</t>
+          <t>04341651827</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -7582,7 +7637,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>VIDA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -7591,20 +7646,20 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>45870</v>
+        <v>45867</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>842857</v>
+        <v>544859</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>45870</v>
+        <v>45867</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>46235</v>
+        <v>46232</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7620,7 +7675,7 @@
       <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
@@ -7631,74 +7686,74 @@
       <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>Olívia Souza</t>
+          <t>Tatiana Ferreira</t>
         </is>
       </c>
       <c r="U30" s="3" t="n">
-        <v>89026012796</v>
+        <v>4341651827</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>9154494</v>
+        <v>98380962025</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>3165.12</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>72.69</v>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Carla Seguros</t>
+        </is>
+      </c>
+      <c r="AB30" s="4" t="n">
+        <v>45867</v>
+      </c>
+      <c r="AC30" s="4" t="n">
+        <v>45867</v>
+      </c>
+      <c r="AD30" s="3" t="n">
+        <v>72.69</v>
+      </c>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>usuario.exemplo</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3" t="n">
         <v>12</v>
-      </c>
-      <c r="Z30" s="3" t="n">
-        <v>379.81</v>
-      </c>
-      <c r="AA30" s="3" t="inlineStr">
-        <is>
-          <t>Corretor Exemplo</t>
-        </is>
-      </c>
-      <c r="AB30" s="4" t="n">
-        <v>45870</v>
-      </c>
-      <c r="AC30" s="4" t="n">
-        <v>45870</v>
-      </c>
-      <c r="AD30" s="3" t="n">
-        <v>379.81</v>
-      </c>
-      <c r="AE30" s="3" t="inlineStr">
-        <is>
-          <t>usuario.exemplo</t>
-        </is>
-      </c>
-      <c r="AF30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="AH30" s="3" t="inlineStr"/>
       <c r="AI30" s="3" t="inlineStr"/>
       <c r="AJ30" s="3" t="n">
-        <v>964618</v>
+        <v>336130</v>
       </c>
       <c r="AK30" s="3" t="inlineStr"/>
       <c r="AL30" s="4" t="n">
-        <v>45870</v>
+        <v>45867</v>
       </c>
       <c r="AM30" s="3" t="inlineStr"/>
       <c r="AN30" s="4" t="n">
-        <v>45870</v>
+        <v>45867</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP30" s="3" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>Cirurgia Geral</t>
+          <t>Radiologia</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
@@ -7708,7 +7763,7 @@
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>9154494</t>
+          <t>9838096</t>
         </is>
       </c>
       <c r="AT30" s="3" t="b">
@@ -7718,7 +7773,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>PROD-004406</t>
+          <t>PROD-004160</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -7727,48 +7782,48 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>4406</v>
+        <v>4160</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>28685289755</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>SAÚDE</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL</t>
+          <t>EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="I31" s="6" t="n">
-        <v>45886</v>
+        <v>45897</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>901247</v>
+        <v>545643</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>45886</v>
+        <v>45897</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>46251</v>
+        <v>46262</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>TETA</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -7784,7 +7839,7 @@
       <c r="P31" s="5" t="inlineStr"/>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R31" s="5" t="inlineStr">
@@ -7795,40 +7850,40 @@
       <c r="S31" s="5" t="inlineStr"/>
       <c r="T31" s="5" t="inlineStr">
         <is>
-          <t>Helena Gomes</t>
+          <t>Rafaela Pereira</t>
         </is>
       </c>
       <c r="U31" s="5" t="n">
-        <v>91846386557</v>
+        <v>28685289755</v>
       </c>
       <c r="V31" s="5" t="n">
-        <v>91217802025</v>
+        <v>1317536</v>
       </c>
       <c r="W31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X31" s="5" t="n">
-        <v>8185.23</v>
+        <v>3443.15</v>
       </c>
       <c r="Y31" s="5" t="n">
         <v>12</v>
       </c>
       <c r="Z31" s="5" t="n">
-        <v>982.23</v>
+        <v>413.18</v>
       </c>
       <c r="AA31" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="AB31" s="6" t="n">
-        <v>45886</v>
+        <v>45897</v>
       </c>
       <c r="AC31" s="6" t="n">
-        <v>45886</v>
+        <v>45897</v>
       </c>
       <c r="AD31" s="5" t="n">
-        <v>982.23</v>
+        <v>413.18</v>
       </c>
       <c r="AE31" s="5" t="inlineStr">
         <is>
@@ -7839,40 +7894,40 @@
         <v>0</v>
       </c>
       <c r="AG31" s="5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH31" s="5" t="inlineStr"/>
       <c r="AI31" s="5" t="inlineStr"/>
       <c r="AJ31" s="5" t="n">
-        <v>905448</v>
+        <v>395720</v>
       </c>
       <c r="AK31" s="5" t="inlineStr"/>
       <c r="AL31" s="6" t="n">
-        <v>45886</v>
+        <v>45897</v>
       </c>
       <c r="AM31" s="5" t="inlineStr"/>
       <c r="AN31" s="6" t="n">
-        <v>45886</v>
+        <v>45897</v>
       </c>
       <c r="AO31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP31" s="5" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AQ31" s="5" t="inlineStr">
         <is>
-          <t>Psiquiatria</t>
+          <t>Dermatologia</t>
         </is>
       </c>
       <c r="AR31" s="5" t="inlineStr">
         <is>
-          <t>EMPRESARIAL - Plano Exemplo</t>
+          <t>EQUIPAMENTOS - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS31" s="5" t="inlineStr">
         <is>
-          <t>9121780</t>
+          <t>1317536</t>
         </is>
       </c>
       <c r="AT31" s="5" t="b">
@@ -7882,7 +7937,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>PROD-004408</t>
+          <t>PROD-004401</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7891,21 +7946,21 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>4408</v>
+        <v>4401</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>91846386557</t>
+          <t>93305172897</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -7915,24 +7970,24 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>45867</v>
+        <v>45884</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>544859</v>
+        <v>505363</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>45867</v>
+        <v>45884</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>46232</v>
+        <v>46249</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>DELT</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7948,7 +8003,7 @@
       <c r="P32" s="3" t="inlineStr"/>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
@@ -7959,40 +8014,40 @@
       <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>Helena Gomes</t>
+          <t>Igor Pereira</t>
         </is>
       </c>
       <c r="U32" s="3" t="n">
-        <v>91846386557</v>
+        <v>93305172897</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>98380962025</v>
+        <v>9693054</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>403.86</v>
+        <v>2231.56</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>72.69</v>
+        <v>669.47</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>45867</v>
+        <v>45884</v>
       </c>
       <c r="AC32" s="4" t="n">
-        <v>45867</v>
+        <v>45884</v>
       </c>
       <c r="AD32" s="3" t="n">
-        <v>72.69</v>
+        <v>669.47</v>
       </c>
       <c r="AE32" s="3" t="inlineStr">
         <is>
@@ -8003,40 +8058,40 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AH32" s="3" t="inlineStr"/>
       <c r="AI32" s="3" t="inlineStr"/>
       <c r="AJ32" s="3" t="n">
-        <v>336130</v>
+        <v>793543</v>
       </c>
       <c r="AK32" s="3" t="inlineStr"/>
       <c r="AL32" s="4" t="n">
-        <v>45867</v>
+        <v>45884</v>
       </c>
       <c r="AM32" s="3" t="inlineStr"/>
       <c r="AN32" s="4" t="n">
-        <v>45867</v>
+        <v>45884</v>
       </c>
       <c r="AO32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP32" s="3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>Psiquiatria</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>RESIDENCIAL - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>9838096</t>
+          <t>9693054</t>
         </is>
       </c>
       <c r="AT32" s="3" t="b">
@@ -8046,7 +8101,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>PROD-004460</t>
+          <t>PROD-004786</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -8055,48 +8110,48 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>4460</v>
+        <v>4786</v>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>24051477053</t>
+          <t>81845184894</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>SAÚDE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I33" s="6" t="n">
-        <v>45897</v>
+        <v>45918</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>545643</v>
+        <v>295124</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>45897</v>
+        <v>45918</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>46262</v>
+        <v>46283</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>TETA</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
@@ -8112,7 +8167,7 @@
       <c r="P33" s="5" t="inlineStr"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr">
@@ -8123,40 +8178,40 @@
       <c r="S33" s="5" t="inlineStr"/>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t>Júlia Rodrigues</t>
+          <t>Eduardo Araújo</t>
         </is>
       </c>
       <c r="U33" s="5" t="n">
-        <v>24051477053</v>
+        <v>81845184894</v>
       </c>
       <c r="V33" s="5" t="n">
-        <v>1317536</v>
+        <v>3686744</v>
       </c>
       <c r="W33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X33" s="5" t="n">
-        <v>3443.15</v>
+        <v>4292.44</v>
       </c>
       <c r="Y33" s="5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Z33" s="5" t="n">
-        <v>413.18</v>
+        <v>858.49</v>
       </c>
       <c r="AA33" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="AB33" s="6" t="n">
-        <v>45897</v>
+        <v>45918</v>
       </c>
       <c r="AC33" s="6" t="n">
-        <v>45897</v>
+        <v>45918</v>
       </c>
       <c r="AD33" s="5" t="n">
-        <v>413.18</v>
+        <v>858.49</v>
       </c>
       <c r="AE33" s="5" t="inlineStr">
         <is>
@@ -8172,35 +8227,35 @@
       <c r="AH33" s="5" t="inlineStr"/>
       <c r="AI33" s="5" t="inlineStr"/>
       <c r="AJ33" s="5" t="n">
-        <v>395720</v>
+        <v>813774</v>
       </c>
       <c r="AK33" s="5" t="inlineStr"/>
       <c r="AL33" s="6" t="n">
-        <v>45897</v>
+        <v>45918</v>
       </c>
       <c r="AM33" s="5" t="inlineStr"/>
       <c r="AN33" s="6" t="n">
-        <v>45897</v>
+        <v>45918</v>
       </c>
       <c r="AO33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP33" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AQ33" s="5" t="inlineStr">
         <is>
-          <t>Clínica Médica</t>
+          <t>Radiologia</t>
         </is>
       </c>
       <c r="AR33" s="5" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS33" s="5" t="inlineStr">
         <is>
-          <t>1317536</t>
+          <t>3686744</t>
         </is>
       </c>
       <c r="AT33" s="5" t="b">
@@ -8210,7 +8265,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>PROD-004701</t>
+          <t>PROD-004788</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -8219,16 +8274,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>4701</v>
+        <v>4788</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>26011939103</t>
+          <t>55460158517</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -8247,20 +8302,20 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>45884</v>
+        <v>45890</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>505363</v>
+        <v>297595</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>45884</v>
+        <v>45890</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>DELT</t>
+          <t>ALFA</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -8276,7 +8331,7 @@
       <c r="P34" s="3" t="inlineStr"/>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
@@ -8287,40 +8342,40 @@
       <c r="S34" s="3" t="inlineStr"/>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>Eduardo Oliveira</t>
+          <t>Helena Araújo</t>
         </is>
       </c>
       <c r="U34" s="3" t="n">
-        <v>26011939103</v>
+        <v>55460158517</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>9693054</v>
+        <v>4234282</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>2231.56</v>
+        <v>4495.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>669.47</v>
+        <v>899.0599999999999</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Bruno Corretor</t>
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>45884</v>
+        <v>45890</v>
       </c>
       <c r="AC34" s="4" t="n">
-        <v>45884</v>
+        <v>45890</v>
       </c>
       <c r="AD34" s="3" t="n">
-        <v>669.47</v>
+        <v>899.0599999999999</v>
       </c>
       <c r="AE34" s="3" t="inlineStr">
         <is>
@@ -8331,30 +8386,30 @@
         <v>0</v>
       </c>
       <c r="AG34" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH34" s="3" t="inlineStr"/>
       <c r="AI34" s="3" t="inlineStr"/>
       <c r="AJ34" s="3" t="n">
-        <v>793543</v>
+        <v>401195</v>
       </c>
       <c r="AK34" s="3" t="inlineStr"/>
       <c r="AL34" s="4" t="n">
-        <v>45884</v>
+        <v>45890</v>
       </c>
       <c r="AM34" s="3" t="inlineStr"/>
       <c r="AN34" s="4" t="n">
-        <v>45884</v>
+        <v>45890</v>
       </c>
       <c r="AO34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP34" s="3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>Pediatria</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
@@ -8364,7 +8419,7 @@
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>9693054</t>
+          <t>4234282</t>
         </is>
       </c>
       <c r="AT34" s="3" t="b">
@@ -8374,7 +8429,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PROD-004731</t>
+          <t>PROD-004793</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -8383,11 +8438,11 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>4731</v>
+        <v>4793</v>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>15313636317</t>
+          <t>20616329451</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -8411,16 +8466,16 @@
         </is>
       </c>
       <c r="I35" s="6" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>423913</v>
+        <v>778557</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
@@ -8451,40 +8506,40 @@
       <c r="S35" s="5" t="inlineStr"/>
       <c r="T35" s="5" t="inlineStr">
         <is>
-          <t>Fernanda Martins</t>
+          <t>Yara Lima</t>
         </is>
       </c>
       <c r="U35" s="5" t="n">
-        <v>15313636317</v>
+        <v>20616329451</v>
       </c>
       <c r="V35" s="5" t="n">
-        <v>3262616</v>
+        <v>1315979</v>
       </c>
       <c r="W35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X35" s="5" t="n">
-        <v>3908.5</v>
+        <v>4137.09</v>
       </c>
       <c r="Y35" s="5" t="n">
         <v>20</v>
       </c>
       <c r="Z35" s="5" t="n">
-        <v>1637.11</v>
+        <v>827.42</v>
       </c>
       <c r="AA35" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="AB35" s="6" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="AC35" s="6" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="AD35" s="5" t="n">
-        <v>1637.11</v>
+        <v>827.42</v>
       </c>
       <c r="AE35" s="5" t="inlineStr">
         <is>
@@ -8495,30 +8550,30 @@
         <v>0</v>
       </c>
       <c r="AG35" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH35" s="5" t="inlineStr"/>
       <c r="AI35" s="5" t="inlineStr"/>
       <c r="AJ35" s="5" t="n">
-        <v>133581</v>
+        <v>114464</v>
       </c>
       <c r="AK35" s="5" t="inlineStr"/>
       <c r="AL35" s="6" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="AM35" s="5" t="inlineStr"/>
       <c r="AN35" s="6" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="AO35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP35" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ35" s="5" t="inlineStr">
         <is>
-          <t>Clínica Médica</t>
+          <t>Oftalmologia</t>
         </is>
       </c>
       <c r="AR35" s="5" t="inlineStr">
@@ -8528,7 +8583,7 @@
       </c>
       <c r="AS35" s="5" t="inlineStr">
         <is>
-          <t>3262616</t>
+          <t>1315979</t>
         </is>
       </c>
       <c r="AT35" s="5" t="b">
@@ -8538,7 +8593,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>PROD-004748</t>
+          <t>PROD-004800</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8547,11 +8602,11 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>4748</v>
+        <v>4800</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>87258874495</t>
+          <t>11435190669</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -8575,16 +8630,16 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>45900</v>
+        <v>45893</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>307099</v>
+        <v>107083</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>45900</v>
+        <v>45893</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -8615,40 +8670,40 @@
       <c r="S36" s="3" t="inlineStr"/>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>Mariana Oliveira</t>
+          <t>Gabriel Costa</t>
         </is>
       </c>
       <c r="U36" s="3" t="n">
-        <v>87258874495</v>
+        <v>11435190669</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>8679757</v>
+        <v>1115992</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>4433.94</v>
+        <v>4244.43</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>20</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>886.79</v>
+        <v>848.89</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>45900</v>
+        <v>45893</v>
       </c>
       <c r="AC36" s="4" t="n">
-        <v>45900</v>
+        <v>45893</v>
       </c>
       <c r="AD36" s="3" t="n">
-        <v>886.79</v>
+        <v>848.89</v>
       </c>
       <c r="AE36" s="3" t="inlineStr">
         <is>
@@ -8659,30 +8714,30 @@
         <v>0</v>
       </c>
       <c r="AG36" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH36" s="3" t="inlineStr"/>
       <c r="AI36" s="3" t="inlineStr"/>
       <c r="AJ36" s="3" t="n">
-        <v>819866</v>
+        <v>420370</v>
       </c>
       <c r="AK36" s="3" t="inlineStr"/>
       <c r="AL36" s="4" t="n">
-        <v>45900</v>
+        <v>45893</v>
       </c>
       <c r="AM36" s="3" t="inlineStr"/>
       <c r="AN36" s="4" t="n">
-        <v>45900</v>
+        <v>45893</v>
       </c>
       <c r="AO36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP36" s="3" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>Cardiologia</t>
+          <t>Neurologia</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
@@ -8692,7 +8747,7 @@
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>8679757</t>
+          <t>1115992</t>
         </is>
       </c>
       <c r="AT36" s="3" t="b">
@@ -8702,7 +8757,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PROD-004756</t>
+          <t>PROD-004801</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -8711,11 +8766,11 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>4756</v>
+        <v>4801</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>71657262849</t>
+          <t>04556110022</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -8739,16 +8794,16 @@
         </is>
       </c>
       <c r="I37" s="6" t="n">
-        <v>45904</v>
+        <v>45891</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>874662</v>
+        <v>217382</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>45904</v>
+        <v>45891</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>46269</v>
+        <v>46256</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
@@ -8779,40 +8834,40 @@
       <c r="S37" s="5" t="inlineStr"/>
       <c r="T37" s="5" t="inlineStr">
         <is>
-          <t>Daniel Martins</t>
+          <t>Lucas Ferreira</t>
         </is>
       </c>
       <c r="U37" s="5" t="n">
-        <v>71657262849</v>
+        <v>4556110022</v>
       </c>
       <c r="V37" s="5" t="n">
-        <v>9280290</v>
+        <v>4856358</v>
       </c>
       <c r="W37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X37" s="5" t="n">
-        <v>3843.36</v>
+        <v>4287.11</v>
       </c>
       <c r="Y37" s="5" t="n">
         <v>20</v>
       </c>
       <c r="Z37" s="5" t="n">
-        <v>5041.73</v>
+        <v>857.42</v>
       </c>
       <c r="AA37" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="AB37" s="6" t="n">
-        <v>45904</v>
+        <v>45891</v>
       </c>
       <c r="AC37" s="6" t="n">
-        <v>45904</v>
+        <v>45891</v>
       </c>
       <c r="AD37" s="5" t="n">
-        <v>5041.73</v>
+        <v>857.42</v>
       </c>
       <c r="AE37" s="5" t="inlineStr">
         <is>
@@ -8823,20 +8878,20 @@
         <v>0</v>
       </c>
       <c r="AG37" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH37" s="5" t="inlineStr"/>
       <c r="AI37" s="5" t="inlineStr"/>
       <c r="AJ37" s="5" t="n">
-        <v>431798</v>
+        <v>390648</v>
       </c>
       <c r="AK37" s="5" t="inlineStr"/>
       <c r="AL37" s="6" t="n">
-        <v>45904</v>
+        <v>45891</v>
       </c>
       <c r="AM37" s="5" t="inlineStr"/>
       <c r="AN37" s="6" t="n">
-        <v>45904</v>
+        <v>45891</v>
       </c>
       <c r="AO37" s="5" t="n">
         <v>1</v>
@@ -8846,7 +8901,7 @@
       </c>
       <c r="AQ37" s="5" t="inlineStr">
         <is>
-          <t>Otorrinolaringologia</t>
+          <t>Cardiologia</t>
         </is>
       </c>
       <c r="AR37" s="5" t="inlineStr">
@@ -8856,7 +8911,7 @@
       </c>
       <c r="AS37" s="5" t="inlineStr">
         <is>
-          <t>9280290</t>
+          <t>4856358</t>
         </is>
       </c>
       <c r="AT37" s="5" t="b">
@@ -8866,7 +8921,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>PROD-004766</t>
+          <t>PROD-004802</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8875,11 +8930,11 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>4766</v>
+        <v>4802</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>62244472126</t>
+          <t>54019380262</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -8903,16 +8958,16 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>45900</v>
+        <v>45909</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>903738</v>
+        <v>307186</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>45900</v>
+        <v>45909</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -8943,40 +8998,40 @@
       <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>Rafaela Lima</t>
+          <t>Lucas Gomes</t>
         </is>
       </c>
       <c r="U38" s="3" t="n">
-        <v>62244472126</v>
+        <v>54019380262</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>8882503</v>
+        <v>4102468</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>3848.65</v>
+        <v>3912.42</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>20</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>769.73</v>
+        <v>782.48</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>45900</v>
+        <v>45909</v>
       </c>
       <c r="AC38" s="4" t="n">
-        <v>45900</v>
+        <v>45909</v>
       </c>
       <c r="AD38" s="3" t="n">
-        <v>769.73</v>
+        <v>782.48</v>
       </c>
       <c r="AE38" s="3" t="inlineStr">
         <is>
@@ -8987,30 +9042,30 @@
         <v>0</v>
       </c>
       <c r="AG38" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AH38" s="3" t="inlineStr"/>
       <c r="AI38" s="3" t="inlineStr"/>
       <c r="AJ38" s="3" t="n">
-        <v>912454</v>
+        <v>860589</v>
       </c>
       <c r="AK38" s="3" t="inlineStr"/>
       <c r="AL38" s="4" t="n">
-        <v>45900</v>
+        <v>45909</v>
       </c>
       <c r="AM38" s="3" t="inlineStr"/>
       <c r="AN38" s="4" t="n">
-        <v>45900</v>
+        <v>45909</v>
       </c>
       <c r="AO38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP38" s="3" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>Cirurgia Geral</t>
+          <t>Psiquiatria</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
@@ -9020,7 +9075,7 @@
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>8882503</t>
+          <t>4102468</t>
         </is>
       </c>
       <c r="AT38" s="3" t="b">
@@ -9030,7 +9085,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>PROD-004768</t>
+          <t>PROD-004805</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -9039,11 +9094,11 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>4768</v>
+        <v>4805</v>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>62003424420</t>
+          <t>39385258001</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -9067,16 +9122,16 @@
         </is>
       </c>
       <c r="I39" s="6" t="n">
-        <v>45889</v>
+        <v>45902</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>467781</v>
+        <v>309817</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>45889</v>
+        <v>45902</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>46254</v>
+        <v>46267</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
@@ -9107,40 +9162,40 @@
       <c r="S39" s="5" t="inlineStr"/>
       <c r="T39" s="5" t="inlineStr">
         <is>
-          <t>Fernanda Costa</t>
+          <t>Mariana Gomes</t>
         </is>
       </c>
       <c r="U39" s="5" t="n">
-        <v>62003424420</v>
+        <v>39385258001</v>
       </c>
       <c r="V39" s="5" t="n">
-        <v>4835183</v>
+        <v>1573416</v>
       </c>
       <c r="W39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X39" s="5" t="n">
-        <v>4243.38</v>
+        <v>4034.93</v>
       </c>
       <c r="Y39" s="5" t="n">
         <v>20</v>
       </c>
       <c r="Z39" s="5" t="n">
-        <v>848.6799999999999</v>
+        <v>806.99</v>
       </c>
       <c r="AA39" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="AB39" s="6" t="n">
-        <v>45889</v>
+        <v>45902</v>
       </c>
       <c r="AC39" s="6" t="n">
-        <v>45889</v>
+        <v>45902</v>
       </c>
       <c r="AD39" s="5" t="n">
-        <v>848.6799999999999</v>
+        <v>806.99</v>
       </c>
       <c r="AE39" s="5" t="inlineStr">
         <is>
@@ -9156,25 +9211,25 @@
       <c r="AH39" s="5" t="inlineStr"/>
       <c r="AI39" s="5" t="inlineStr"/>
       <c r="AJ39" s="5" t="n">
-        <v>377347</v>
+        <v>283402</v>
       </c>
       <c r="AK39" s="5" t="inlineStr"/>
       <c r="AL39" s="6" t="n">
-        <v>45889</v>
+        <v>45902</v>
       </c>
       <c r="AM39" s="5" t="inlineStr"/>
       <c r="AN39" s="6" t="n">
-        <v>45889</v>
+        <v>45902</v>
       </c>
       <c r="AO39" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP39" s="5" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="AQ39" s="5" t="inlineStr">
         <is>
-          <t>Anestesiologia</t>
+          <t>Dermatologia</t>
         </is>
       </c>
       <c r="AR39" s="5" t="inlineStr">
@@ -9184,7 +9239,7 @@
       </c>
       <c r="AS39" s="5" t="inlineStr">
         <is>
-          <t>4835183</t>
+          <t>1573416</t>
         </is>
       </c>
       <c r="AT39" s="5" t="b">
@@ -9194,7 +9249,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>PROD-004770</t>
+          <t>PROD-004823</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9203,11 +9258,11 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4770</v>
+        <v>4823</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>45547813767</t>
+          <t>96631931491</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -9231,16 +9286,16 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>45920</v>
+        <v>45916</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>534534</v>
+        <v>189781</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>45920</v>
+        <v>45916</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>46285</v>
+        <v>46281</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -9271,40 +9326,40 @@
       <c r="S40" s="3" t="inlineStr"/>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>Ana Oliveira</t>
+          <t>Tatiana Barbosa</t>
         </is>
       </c>
       <c r="U40" s="3" t="n">
-        <v>45547813767</v>
+        <v>96631931491</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>9625375</v>
+        <v>7233232</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>4191.78</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>20</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>838.36</v>
+        <v>848.27</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>45920</v>
+        <v>45916</v>
       </c>
       <c r="AC40" s="4" t="n">
-        <v>45920</v>
+        <v>45916</v>
       </c>
       <c r="AD40" s="3" t="n">
-        <v>838.36</v>
+        <v>848.27</v>
       </c>
       <c r="AE40" s="3" t="inlineStr">
         <is>
@@ -9320,25 +9375,25 @@
       <c r="AH40" s="3" t="inlineStr"/>
       <c r="AI40" s="3" t="inlineStr"/>
       <c r="AJ40" s="3" t="n">
-        <v>909681</v>
+        <v>536716</v>
       </c>
       <c r="AK40" s="3" t="inlineStr"/>
       <c r="AL40" s="4" t="n">
-        <v>45920</v>
+        <v>45916</v>
       </c>
       <c r="AM40" s="3" t="inlineStr"/>
       <c r="AN40" s="4" t="n">
-        <v>45920</v>
+        <v>45916</v>
       </c>
       <c r="AO40" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP40" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>Psiquiatria</t>
+          <t>Oftalmologia</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
@@ -9348,7 +9403,7 @@
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>9625375</t>
+          <t>7233232</t>
         </is>
       </c>
       <c r="AT40" s="3" t="b">
@@ -9358,7 +9413,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>PROD-004774</t>
+          <t>PROD-004831</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -9367,11 +9422,11 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>4774</v>
+        <v>4831</v>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>37562890028</t>
+          <t>66978480184</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -9395,16 +9450,16 @@
         </is>
       </c>
       <c r="I41" s="6" t="n">
-        <v>45898</v>
+        <v>45908</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>619869</v>
+        <v>961915</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>45898</v>
+        <v>45908</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>46263</v>
+        <v>46273</v>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
@@ -9435,40 +9490,40 @@
       <c r="S41" s="5" t="inlineStr"/>
       <c r="T41" s="5" t="inlineStr">
         <is>
-          <t>Ana Oliveira</t>
+          <t>Yara Souza</t>
         </is>
       </c>
       <c r="U41" s="5" t="n">
-        <v>37562890028</v>
+        <v>66978480184</v>
       </c>
       <c r="V41" s="5" t="n">
-        <v>5295429</v>
+        <v>3630064</v>
       </c>
       <c r="W41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X41" s="5" t="n">
-        <v>3578.73</v>
+        <v>3755.46</v>
       </c>
       <c r="Y41" s="5" t="n">
         <v>20</v>
       </c>
       <c r="Z41" s="5" t="n">
-        <v>715.75</v>
+        <v>751.09</v>
       </c>
       <c r="AA41" s="5" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Equipe Digital</t>
         </is>
       </c>
       <c r="AB41" s="6" t="n">
-        <v>45898</v>
+        <v>45908</v>
       </c>
       <c r="AC41" s="6" t="n">
-        <v>45898</v>
+        <v>45908</v>
       </c>
       <c r="AD41" s="5" t="n">
-        <v>715.75</v>
+        <v>751.09</v>
       </c>
       <c r="AE41" s="5" t="inlineStr">
         <is>
@@ -9484,25 +9539,25 @@
       <c r="AH41" s="5" t="inlineStr"/>
       <c r="AI41" s="5" t="inlineStr"/>
       <c r="AJ41" s="5" t="n">
-        <v>375330</v>
+        <v>558273</v>
       </c>
       <c r="AK41" s="5" t="inlineStr"/>
       <c r="AL41" s="6" t="n">
-        <v>45898</v>
+        <v>45908</v>
       </c>
       <c r="AM41" s="5" t="inlineStr"/>
       <c r="AN41" s="6" t="n">
-        <v>45898</v>
+        <v>45908</v>
       </c>
       <c r="AO41" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AP41" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AQ41" s="5" t="inlineStr">
         <is>
-          <t>Psiquiatria</t>
+          <t>Cirurgia Geral</t>
         </is>
       </c>
       <c r="AR41" s="5" t="inlineStr">
@@ -9512,7 +9567,7 @@
       </c>
       <c r="AS41" s="5" t="inlineStr">
         <is>
-          <t>5295429</t>
+          <t>3630064</t>
         </is>
       </c>
       <c r="AT41" s="5" t="b">
@@ -9522,7 +9577,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>PROD-004776</t>
+          <t>PROD-004835</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9531,48 +9586,48 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>4776</v>
+        <v>4835</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>70335211039</t>
+          <t>22535841438</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>VIAGEM</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS</t>
+          <t>AUTOMÓVEL</t>
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>45906</v>
+        <v>45834</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>336446</v>
+        <v>280510</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>45906</v>
+        <v>45834</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>46271</v>
+        <v>46199</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>ALFA</t>
+          <t>ZETA</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -9599,40 +9654,40 @@
       <c r="S42" s="3" t="inlineStr"/>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>Daniel Barbosa</t>
+          <t>Ana Ferreira</t>
         </is>
       </c>
       <c r="U42" s="3" t="n">
-        <v>70335211039</v>
+        <v>22535841438</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>1430716</v>
+        <v>37426102025</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>4592.43</v>
+        <v>5218.51</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>15</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>688.86</v>
+        <v>782.78</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>Corretor Exemplo</t>
+          <t>Diego Comercial</t>
         </is>
       </c>
       <c r="AB42" s="4" t="n">
-        <v>45906</v>
+        <v>45834</v>
       </c>
       <c r="AC42" s="4" t="n">
-        <v>45906</v>
+        <v>45834</v>
       </c>
       <c r="AD42" s="3" t="n">
-        <v>688.86</v>
+        <v>782.78</v>
       </c>
       <c r="AE42" s="3" t="inlineStr">
         <is>
@@ -9643,48 +9698,212 @@
         <v>0</v>
       </c>
       <c r="AG42" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AH42" s="3" t="inlineStr"/>
       <c r="AI42" s="3" t="inlineStr"/>
       <c r="AJ42" s="3" t="n">
-        <v>234921</v>
+        <v>112535</v>
       </c>
       <c r="AK42" s="3" t="inlineStr"/>
       <c r="AL42" s="4" t="n">
-        <v>45906</v>
+        <v>45834</v>
       </c>
       <c r="AM42" s="3" t="inlineStr"/>
       <c r="AN42" s="4" t="n">
-        <v>45906</v>
+        <v>45834</v>
       </c>
       <c r="AO42" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP42" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>Otorrinolaringologia</t>
+          <t>Anestesiologia</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS - Plano Exemplo</t>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>1430716</t>
+          <t>3742610</t>
         </is>
       </c>
       <c r="AT42" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>PROD-004839</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>RptAnaliseProducao.xlsx</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>4839</v>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>39385258001</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>ALFA</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>AUTOMÓVEL</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>AUTOMÓVEL</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>45902</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>309817</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>45902</v>
+      </c>
+      <c r="L43" s="6" t="n">
+        <v>46267</v>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>ALFA</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>Ativa</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>Grupo 1</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>APÓLICE</t>
+        </is>
+      </c>
+      <c r="S43" s="5" t="inlineStr"/>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>Mariana Gomes</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="n">
+        <v>39385258001</v>
+      </c>
+      <c r="V43" s="5" t="n">
+        <v>1573416</v>
+      </c>
+      <c r="W43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="5" t="n">
+        <v>4034.93</v>
+      </c>
+      <c r="Y43" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z43" s="5" t="n">
+        <v>806.99</v>
+      </c>
+      <c r="AA43" s="5" t="inlineStr">
+        <is>
+          <t>Equipe Digital</t>
+        </is>
+      </c>
+      <c r="AB43" s="6" t="n">
+        <v>45902</v>
+      </c>
+      <c r="AC43" s="6" t="n">
+        <v>45902</v>
+      </c>
+      <c r="AD43" s="5" t="n">
+        <v>806.99</v>
+      </c>
+      <c r="AE43" s="5" t="inlineStr">
+        <is>
+          <t>usuario.exemplo</t>
+        </is>
+      </c>
+      <c r="AF43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH43" s="5" t="inlineStr"/>
+      <c r="AI43" s="5" t="inlineStr"/>
+      <c r="AJ43" s="5" t="n">
+        <v>283402</v>
+      </c>
+      <c r="AK43" s="5" t="inlineStr"/>
+      <c r="AL43" s="6" t="n">
+        <v>45902</v>
+      </c>
+      <c r="AM43" s="5" t="inlineStr"/>
+      <c r="AN43" s="6" t="n">
+        <v>45902</v>
+      </c>
+      <c r="AO43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ43" s="5" t="inlineStr">
+        <is>
+          <t>Dermatologia</t>
+        </is>
+      </c>
+      <c r="AR43" s="5" t="inlineStr">
+        <is>
+          <t>AUTOMÓVEL - Plano Exemplo</t>
+        </is>
+      </c>
+      <c r="AS43" s="5" t="inlineStr">
+        <is>
+          <t>1573416</t>
+        </is>
+      </c>
+      <c r="AT43" s="5" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT42"/>
+  <autoFilter ref="A1:AT43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>